--- a/sourcedat.xlsx
+++ b/sourcedat.xlsx
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="6136" uniqueCount="1737">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="6792" uniqueCount="1737">
   <si>
     <t xml:space="preserve">human_mean</t>
   </si>
@@ -16618,9 +16618,9 @@
     <col min="2" max="2" width="11.99" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
     <col min="3" max="3" width="8.14" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
     <col min="4" max="4" width="22.86" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
-    <col min="6" max="6" width="11.71" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
-    <col min="7" max="7" width="16.29" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
-    <col min="8" max="8" width="22.86" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="6" max="6" width="11.7109375" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="7" max="7" width="16.28515625" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="8" max="8" width="22.85546875" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
     <col min="10" max="10" width="67.14" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
     <col min="11" max="11" width="11.99" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
     <col min="12" max="12" width="16.29" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
@@ -16636,6 +16636,7 @@
       <c r="D1" s="0" t="s">
         <v>34</v>
       </c>
+      <c r="F1" s="0"/>
       <c r="G1" s="0" t="s">
         <v>57</v>
       </c>
@@ -16668,8 +16669,8 @@
       <c r="G2" s="0" t="s">
         <v>1393</v>
       </c>
-      <c r="H2" s="0" t="n">
-        <v>0</v>
+      <c r="H2" s="0">
+        <v>0.0054972513743128436</v>
       </c>
       <c r="J2" s="0" t="s">
         <v>201</v>
@@ -16700,8 +16701,8 @@
       <c r="G3" s="0" t="s">
         <v>1394</v>
       </c>
-      <c r="H3" s="0" t="n">
-        <v>0</v>
+      <c r="H3" s="0">
+        <v>0.0054972513743128436</v>
       </c>
       <c r="J3" s="0" t="s">
         <v>203</v>
@@ -16732,8 +16733,8 @@
       <c r="G4" s="0" t="s">
         <v>1397</v>
       </c>
-      <c r="H4" s="0" t="n">
-        <v>0</v>
+      <c r="H4" s="0">
+        <v>0.0054972513743128436</v>
       </c>
       <c r="J4" s="0" t="s">
         <v>205</v>
@@ -16764,8 +16765,8 @@
       <c r="G5" s="0" t="s">
         <v>1398</v>
       </c>
-      <c r="H5" s="0" t="n">
-        <v>0</v>
+      <c r="H5" s="0">
+        <v>0.0054972513743128436</v>
       </c>
       <c r="J5" s="0" t="s">
         <v>207</v>
@@ -16796,8 +16797,8 @@
       <c r="G6" s="0" t="s">
         <v>1400</v>
       </c>
-      <c r="H6" s="0" t="n">
-        <v>0</v>
+      <c r="H6" s="0">
+        <v>0.0054972513743128436</v>
       </c>
       <c r="J6" s="0" t="s">
         <v>209</v>
@@ -16828,8 +16829,8 @@
       <c r="G7" s="0" t="s">
         <v>1401</v>
       </c>
-      <c r="H7" s="0" t="n">
-        <v>0</v>
+      <c r="H7" s="0">
+        <v>0.0054972513743128436</v>
       </c>
       <c r="J7" s="0" t="s">
         <v>211</v>
@@ -16860,8 +16861,8 @@
       <c r="G8" s="0" t="s">
         <v>1402</v>
       </c>
-      <c r="H8" s="0" t="n">
-        <v>0</v>
+      <c r="H8" s="0">
+        <v>0.0054972513743128436</v>
       </c>
       <c r="J8" s="0" t="s">
         <v>213</v>
@@ -16892,8 +16893,8 @@
       <c r="G9" s="0" t="s">
         <v>1404</v>
       </c>
-      <c r="H9" s="0" t="n">
-        <v>0</v>
+      <c r="H9" s="0">
+        <v>0.0054972513743128436</v>
       </c>
       <c r="J9" s="0" t="s">
         <v>215</v>
@@ -16924,8 +16925,8 @@
       <c r="G10" s="0" t="s">
         <v>1406</v>
       </c>
-      <c r="H10" s="0" t="n">
-        <v>0</v>
+      <c r="H10" s="0">
+        <v>0.0054972513743128436</v>
       </c>
       <c r="J10" s="0" t="s">
         <v>216</v>
@@ -16956,8 +16957,8 @@
       <c r="G11" s="0" t="s">
         <v>1408</v>
       </c>
-      <c r="H11" s="0" t="n">
-        <v>0</v>
+      <c r="H11" s="0">
+        <v>0.0054972513743128436</v>
       </c>
       <c r="J11" s="0" t="s">
         <v>218</v>
@@ -16988,8 +16989,8 @@
       <c r="G12" s="0" t="s">
         <v>1410</v>
       </c>
-      <c r="H12" s="0" t="n">
-        <v>0</v>
+      <c r="H12" s="0">
+        <v>0.0054972513743128436</v>
       </c>
       <c r="J12" s="0" t="s">
         <v>220</v>
@@ -17014,6 +17015,7 @@
       <c r="G13" s="0" t="s">
         <v>1412</v>
       </c>
+      <c r="H13" s="0"/>
       <c r="J13" s="0" t="s">
         <v>222</v>
       </c>
@@ -19093,9 +19095,9 @@
     <col min="2" max="2" width="11.99" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
     <col min="3" max="3" width="8.14" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
     <col min="4" max="4" width="22.86" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
-    <col min="6" max="6" width="11.71" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
-    <col min="7" max="7" width="16.29" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
-    <col min="8" max="8" width="22.86" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="6" max="6" width="11.7109375" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="7" max="7" width="16.28515625" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="8" max="8" width="22.85546875" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
     <col min="10" max="10" width="67.14" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
     <col min="11" max="11" width="11.99" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
     <col min="12" max="12" width="16.29" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
@@ -19111,6 +19113,7 @@
       <c r="D1" s="0" t="s">
         <v>34</v>
       </c>
+      <c r="F1" s="0"/>
       <c r="G1" s="0" t="s">
         <v>57</v>
       </c>
@@ -19143,8 +19146,8 @@
       <c r="G2" s="0" t="s">
         <v>1435</v>
       </c>
-      <c r="H2" s="0" t="n">
-        <v>0</v>
+      <c r="H2" s="0">
+        <v>0.0054972513743128436</v>
       </c>
       <c r="J2" s="0" t="s">
         <v>201</v>
@@ -19175,8 +19178,8 @@
       <c r="G3" s="0" t="s">
         <v>1437</v>
       </c>
-      <c r="H3" s="0" t="n">
-        <v>0</v>
+      <c r="H3" s="0">
+        <v>0.0054972513743128436</v>
       </c>
       <c r="J3" s="0" t="s">
         <v>203</v>
@@ -19207,8 +19210,8 @@
       <c r="G4" s="0" t="s">
         <v>1439</v>
       </c>
-      <c r="H4" s="0" t="n">
-        <v>0</v>
+      <c r="H4" s="0">
+        <v>0.0054972513743128436</v>
       </c>
       <c r="J4" s="0" t="s">
         <v>205</v>
@@ -19239,8 +19242,8 @@
       <c r="G5" s="0" t="s">
         <v>1441</v>
       </c>
-      <c r="H5" s="0" t="n">
-        <v>0</v>
+      <c r="H5" s="0">
+        <v>0.0054972513743128436</v>
       </c>
       <c r="J5" s="0" t="s">
         <v>207</v>
@@ -19271,8 +19274,8 @@
       <c r="G6" s="0" t="s">
         <v>1443</v>
       </c>
-      <c r="H6" s="0" t="n">
-        <v>0</v>
+      <c r="H6" s="0">
+        <v>0.0054972513743128436</v>
       </c>
       <c r="J6" s="0" t="s">
         <v>209</v>
@@ -19303,8 +19306,8 @@
       <c r="G7" s="0" t="s">
         <v>1445</v>
       </c>
-      <c r="H7" s="0" t="n">
-        <v>0</v>
+      <c r="H7" s="0">
+        <v>0.0054972513743128436</v>
       </c>
       <c r="J7" s="0" t="s">
         <v>211</v>
@@ -19335,8 +19338,8 @@
       <c r="G8" s="0" t="s">
         <v>1446</v>
       </c>
-      <c r="H8" s="0" t="n">
-        <v>0</v>
+      <c r="H8" s="0">
+        <v>0.0054972513743128436</v>
       </c>
       <c r="J8" s="0" t="s">
         <v>213</v>
@@ -19367,8 +19370,8 @@
       <c r="G9" s="0" t="s">
         <v>1448</v>
       </c>
-      <c r="H9" s="0" t="n">
-        <v>0</v>
+      <c r="H9" s="0">
+        <v>0.0054972513743128436</v>
       </c>
       <c r="J9" s="0" t="s">
         <v>215</v>
@@ -19399,8 +19402,8 @@
       <c r="G10" s="0" t="s">
         <v>1451</v>
       </c>
-      <c r="H10" s="0" t="n">
-        <v>0</v>
+      <c r="H10" s="0">
+        <v>0.0054972513743128436</v>
       </c>
       <c r="J10" s="0" t="s">
         <v>216</v>
@@ -19431,8 +19434,8 @@
       <c r="G11" s="0" t="s">
         <v>1453</v>
       </c>
-      <c r="H11" s="0" t="n">
-        <v>0</v>
+      <c r="H11" s="0">
+        <v>0.0054972513743128436</v>
       </c>
       <c r="J11" s="0" t="s">
         <v>218</v>
@@ -19463,8 +19466,8 @@
       <c r="G12" s="0" t="s">
         <v>1455</v>
       </c>
-      <c r="H12" s="0" t="n">
-        <v>0</v>
+      <c r="H12" s="0">
+        <v>0.0054972513743128436</v>
       </c>
       <c r="J12" s="0" t="s">
         <v>220</v>
@@ -19489,6 +19492,7 @@
       <c r="G13" s="0" t="s">
         <v>1457</v>
       </c>
+      <c r="H13" s="0"/>
       <c r="J13" s="0" t="s">
         <v>222</v>
       </c>
@@ -21794,76 +21798,94 @@
   <sheetFormatPr defaultColWidth="8.6953125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="17" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
-    <col min="2" max="2" width="20.57" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
-    <col min="3" max="3" width="22.86" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="2" max="2" width="20.5703125" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="3" max="3" width="22.85546875" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
     <col min="5" max="5" width="17" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
-    <col min="6" max="6" width="20.57" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
-    <col min="7" max="7" width="22.86" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="6" max="6" width="20.5703125" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="7" max="7" width="22.85546875" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
     <col min="9" max="9" width="17" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
-    <col min="10" max="10" width="20.57" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
-    <col min="11" max="11" width="22.86" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="10" max="10" width="20.5703125" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="11" max="11" width="22.85546875" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
     <col min="13" max="13" width="17" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
-    <col min="14" max="14" width="20.57" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
-    <col min="15" max="15" width="22.86" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="14" max="14" width="20.5703125" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="15" max="15" width="22.85546875" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
     <col min="17" max="17" width="17" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
-    <col min="18" max="18" width="20.57" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
-    <col min="19" max="19" width="22.86" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="18" max="18" width="20.5703125" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="19" max="19" width="22.85546875" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
     <col min="21" max="21" width="17" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
-    <col min="22" max="22" width="20.57" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
-    <col min="23" max="23" width="22.86" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="22" max="22" width="20.5703125" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="23" max="23" width="22.85546875" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
         <v>1506</v>
       </c>
+      <c r="B1" s="0"/>
+      <c r="C1" s="0"/>
       <c r="E1" s="0" t="s">
         <v>1507</v>
       </c>
+      <c r="F1" s="0"/>
+      <c r="G1" s="0"/>
       <c r="I1" s="0" t="s">
         <v>1508</v>
       </c>
+      <c r="J1" s="0"/>
+      <c r="K1" s="0"/>
       <c r="M1" s="0" t="s">
         <v>1509</v>
       </c>
+      <c r="N1" s="0"/>
+      <c r="O1" s="0"/>
       <c r="Q1" s="0" t="s">
         <v>1510</v>
       </c>
+      <c r="R1" s="0"/>
+      <c r="S1" s="0"/>
       <c r="U1" s="0" t="s">
         <v>1511</v>
       </c>
+      <c r="V1" s="0"/>
+      <c r="W1" s="0"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="0"/>
       <c r="B2" s="0" t="s">
         <v>1512</v>
       </c>
       <c r="C2" s="0" t="s">
         <v>34</v>
       </c>
+      <c r="E2" s="0"/>
       <c r="F2" s="0" t="s">
         <v>1512</v>
       </c>
       <c r="G2" s="0" t="s">
         <v>34</v>
       </c>
+      <c r="I2" s="0"/>
       <c r="J2" s="0" t="s">
         <v>1512</v>
       </c>
       <c r="K2" s="0" t="s">
         <v>34</v>
       </c>
+      <c r="M2" s="0"/>
       <c r="N2" s="0" t="s">
         <v>1512</v>
       </c>
       <c r="O2" s="0" t="s">
         <v>34</v>
       </c>
+      <c r="Q2" s="0"/>
       <c r="R2" s="0" t="s">
         <v>1512</v>
       </c>
       <c r="S2" s="0" t="s">
         <v>34</v>
       </c>
+      <c r="U2" s="0"/>
       <c r="V2" s="0" t="s">
         <v>1512</v>
       </c>
@@ -21875,672 +21897,672 @@
       <c r="A3" s="0" t="s">
         <v>1513</v>
       </c>
-      <c r="B3" s="0" t="n">
-        <v>13.75</v>
-      </c>
-      <c r="C3" s="0" t="n">
-        <v>0</v>
+      <c r="B3" s="0">
+        <v>13.750000000000002</v>
+      </c>
+      <c r="C3" s="0">
+        <v>0.004995004995004995</v>
       </c>
       <c r="E3" s="0" t="s">
         <v>1513</v>
       </c>
-      <c r="F3" s="0" t="n">
-        <v>6.66666666666667</v>
-      </c>
-      <c r="G3" s="0" t="n">
-        <v>0.01</v>
+      <c r="F3" s="0">
+        <v>6.666666666666667</v>
+      </c>
+      <c r="G3" s="0">
+        <v>0.024975024975024976</v>
       </c>
       <c r="I3" s="0" t="s">
         <v>1513</v>
       </c>
-      <c r="J3" s="0" t="n">
-        <v>15.8333333333333</v>
-      </c>
-      <c r="K3" s="0" t="n">
-        <v>0</v>
+      <c r="J3" s="0">
+        <v>15.833333333333332</v>
+      </c>
+      <c r="K3" s="0">
+        <v>0.004995004995004995</v>
       </c>
       <c r="M3" s="0" t="s">
         <v>1513</v>
       </c>
-      <c r="N3" s="0" t="n">
-        <v>7.91666666666667</v>
-      </c>
-      <c r="O3" s="0" t="n">
-        <v>0</v>
+      <c r="N3" s="0">
+        <v>7.9166666666666661</v>
+      </c>
+      <c r="O3" s="0">
+        <v>0.004995004995004995</v>
       </c>
       <c r="Q3" s="0" t="s">
         <v>1513</v>
       </c>
-      <c r="R3" s="0" t="n">
+      <c r="R3" s="0">
         <v>20</v>
       </c>
-      <c r="S3" s="0" t="n">
-        <v>0</v>
+      <c r="S3" s="0">
+        <v>0.004995004995004995</v>
       </c>
       <c r="U3" s="0" t="s">
         <v>1513</v>
       </c>
-      <c r="V3" s="0" t="n">
-        <v>4.58333333333333</v>
-      </c>
-      <c r="W3" s="0" t="n">
-        <v>0.41</v>
+      <c r="V3" s="0">
+        <v>4.583333333333333</v>
+      </c>
+      <c r="W3" s="0">
+        <v>0.75424575424575424</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
         <v>1514</v>
       </c>
-      <c r="B4" s="0" t="n">
+      <c r="B4" s="0">
         <v>31.25</v>
       </c>
-      <c r="C4" s="0" t="n">
-        <v>0</v>
+      <c r="C4" s="0">
+        <v>0.004995004995004995</v>
       </c>
       <c r="E4" s="0" t="s">
         <v>1514</v>
       </c>
-      <c r="F4" s="0" t="n">
-        <v>25.8333333333333</v>
-      </c>
-      <c r="G4" s="0" t="n">
-        <v>0</v>
+      <c r="F4" s="0">
+        <v>25.833333333333336</v>
+      </c>
+      <c r="G4" s="0">
+        <v>0.004995004995004995</v>
       </c>
       <c r="I4" s="0" t="s">
         <v>1514</v>
       </c>
-      <c r="J4" s="0" t="n">
-        <v>28.3333333333333</v>
-      </c>
-      <c r="K4" s="0" t="n">
-        <v>0</v>
+      <c r="J4" s="0">
+        <v>28.333333333333332</v>
+      </c>
+      <c r="K4" s="0">
+        <v>0.004995004995004995</v>
       </c>
       <c r="M4" s="0" t="s">
         <v>1514</v>
       </c>
-      <c r="N4" s="0" t="n">
+      <c r="N4" s="0">
         <v>20</v>
       </c>
-      <c r="O4" s="0" t="n">
-        <v>0</v>
+      <c r="O4" s="0">
+        <v>0.004995004995004995</v>
       </c>
       <c r="Q4" s="0" t="s">
         <v>1514</v>
       </c>
-      <c r="R4" s="0" t="n">
+      <c r="R4" s="0">
         <v>32.5</v>
       </c>
-      <c r="S4" s="0" t="n">
-        <v>0</v>
+      <c r="S4" s="0">
+        <v>0.004995004995004995</v>
       </c>
       <c r="U4" s="0" t="s">
         <v>1514</v>
       </c>
-      <c r="V4" s="0" t="n">
-        <v>14.1666666666667</v>
-      </c>
-      <c r="W4" s="0" t="n">
-        <v>0</v>
+      <c r="V4" s="0">
+        <v>14.166666666666666</v>
+      </c>
+      <c r="W4" s="0">
+        <v>0.004995004995004995</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
         <v>1515</v>
       </c>
-      <c r="B5" s="0" t="n">
-        <v>77.0833333333333</v>
-      </c>
-      <c r="C5" s="0" t="n">
-        <v>0</v>
+      <c r="B5" s="0">
+        <v>77.083333333333343</v>
+      </c>
+      <c r="C5" s="0">
+        <v>0.004995004995004995</v>
       </c>
       <c r="E5" s="0" t="s">
         <v>1515</v>
       </c>
-      <c r="F5" s="0" t="n">
-        <v>64.1666666666667</v>
-      </c>
-      <c r="G5" s="0" t="n">
-        <v>0</v>
+      <c r="F5" s="0">
+        <v>64.166666666666672</v>
+      </c>
+      <c r="G5" s="0">
+        <v>0.004995004995004995</v>
       </c>
       <c r="I5" s="0" t="s">
         <v>1515</v>
       </c>
-      <c r="J5" s="0" t="n">
-        <v>55.4166666666667</v>
-      </c>
-      <c r="K5" s="0" t="n">
-        <v>0</v>
+      <c r="J5" s="0">
+        <v>55.416666666666671</v>
+      </c>
+      <c r="K5" s="0">
+        <v>0.004995004995004995</v>
       </c>
       <c r="M5" s="0" t="s">
         <v>1515</v>
       </c>
-      <c r="N5" s="0" t="n">
-        <v>51.25</v>
-      </c>
-      <c r="O5" s="0" t="n">
-        <v>0</v>
+      <c r="N5" s="0">
+        <v>51.249999999999993</v>
+      </c>
+      <c r="O5" s="0">
+        <v>0.004995004995004995</v>
       </c>
       <c r="Q5" s="0" t="s">
         <v>1515</v>
       </c>
-      <c r="R5" s="0" t="n">
-        <v>39.1666666666667</v>
-      </c>
-      <c r="S5" s="0" t="n">
-        <v>0</v>
+      <c r="R5" s="0">
+        <v>39.166666666666664</v>
+      </c>
+      <c r="S5" s="0">
+        <v>0.004995004995004995</v>
       </c>
       <c r="U5" s="0" t="s">
         <v>1515</v>
       </c>
-      <c r="V5" s="0" t="n">
+      <c r="V5" s="0">
         <v>18.75</v>
       </c>
-      <c r="W5" s="0" t="n">
-        <v>0</v>
+      <c r="W5" s="0">
+        <v>0.004995004995004995</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
         <v>1516</v>
       </c>
-      <c r="B6" s="0" t="n">
+      <c r="B6" s="0">
         <v>92.5</v>
       </c>
-      <c r="C6" s="0" t="n">
-        <v>0</v>
+      <c r="C6" s="0">
+        <v>0.004995004995004995</v>
       </c>
       <c r="E6" s="0" t="s">
         <v>1516</v>
       </c>
-      <c r="F6" s="0" t="n">
-        <v>79.5833333333333</v>
-      </c>
-      <c r="G6" s="0" t="n">
-        <v>0</v>
+      <c r="F6" s="0">
+        <v>79.583333333333329</v>
+      </c>
+      <c r="G6" s="0">
+        <v>0.004995004995004995</v>
       </c>
       <c r="I6" s="0" t="s">
         <v>1516</v>
       </c>
-      <c r="J6" s="0" t="n">
+      <c r="J6" s="0">
         <v>73.75</v>
       </c>
-      <c r="K6" s="0" t="n">
-        <v>0</v>
+      <c r="K6" s="0">
+        <v>0.004995004995004995</v>
       </c>
       <c r="M6" s="0" t="s">
         <v>1516</v>
       </c>
-      <c r="N6" s="0" t="n">
+      <c r="N6" s="0">
         <v>58.75</v>
       </c>
-      <c r="O6" s="0" t="n">
-        <v>0</v>
+      <c r="O6" s="0">
+        <v>0.004995004995004995</v>
       </c>
       <c r="Q6" s="0" t="s">
         <v>1516</v>
       </c>
-      <c r="R6" s="0" t="n">
-        <v>55</v>
-      </c>
-      <c r="S6" s="0" t="n">
-        <v>0</v>
+      <c r="R6" s="0">
+        <v>55.000000000000007</v>
+      </c>
+      <c r="S6" s="0">
+        <v>0.004995004995004995</v>
       </c>
       <c r="U6" s="0" t="s">
         <v>1516</v>
       </c>
-      <c r="V6" s="0" t="n">
-        <v>29.1666666666667</v>
-      </c>
-      <c r="W6" s="0" t="n">
-        <v>0</v>
+      <c r="V6" s="0">
+        <v>29.166666666666668</v>
+      </c>
+      <c r="W6" s="0">
+        <v>0.004995004995004995</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
         <v>1517</v>
       </c>
-      <c r="B7" s="0" t="n">
-        <v>10.8333333333333</v>
-      </c>
-      <c r="C7" s="0" t="n">
-        <v>0</v>
+      <c r="B7" s="0">
+        <v>10.833333333333334</v>
+      </c>
+      <c r="C7" s="0">
+        <v>0.004995004995004995</v>
       </c>
       <c r="E7" s="0" t="s">
         <v>1517</v>
       </c>
-      <c r="F7" s="0" t="n">
+      <c r="F7" s="0">
         <v>12.5</v>
       </c>
-      <c r="G7" s="0" t="n">
-        <v>0</v>
+      <c r="G7" s="0">
+        <v>0.004995004995004995</v>
       </c>
       <c r="I7" s="0" t="s">
         <v>1517</v>
       </c>
-      <c r="J7" s="0" t="n">
-        <v>21.6666666666667</v>
-      </c>
-      <c r="K7" s="0" t="n">
-        <v>0</v>
+      <c r="J7" s="0">
+        <v>21.666666666666668</v>
+      </c>
+      <c r="K7" s="0">
+        <v>0.004995004995004995</v>
       </c>
       <c r="M7" s="0" t="s">
         <v>1517</v>
       </c>
-      <c r="N7" s="0" t="n">
-        <v>9.58333333333333</v>
-      </c>
-      <c r="O7" s="0" t="n">
-        <v>0</v>
+      <c r="N7" s="0">
+        <v>9.5833333333333339</v>
+      </c>
+      <c r="O7" s="0">
+        <v>0.004995004995004995</v>
       </c>
       <c r="Q7" s="0" t="s">
         <v>1517</v>
       </c>
-      <c r="R7" s="0" t="n">
-        <v>18.3333333333333</v>
-      </c>
-      <c r="S7" s="0" t="n">
-        <v>0</v>
+      <c r="R7" s="0">
+        <v>18.333333333333332</v>
+      </c>
+      <c r="S7" s="0">
+        <v>0.004995004995004995</v>
       </c>
       <c r="U7" s="0" t="s">
         <v>1517</v>
       </c>
-      <c r="V7" s="0" t="n">
-        <v>4.16666666666667</v>
-      </c>
-      <c r="W7" s="0" t="n">
-        <v>0.775</v>
+      <c r="V7" s="0">
+        <v>4.1666666666666661</v>
+      </c>
+      <c r="W7" s="0">
+        <v>1.2187812187812188</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
         <v>1518</v>
       </c>
-      <c r="B8" s="0" t="n">
+      <c r="B8" s="0">
         <v>25</v>
       </c>
-      <c r="C8" s="0" t="n">
-        <v>0</v>
+      <c r="C8" s="0">
+        <v>0.004995004995004995</v>
       </c>
       <c r="E8" s="0" t="s">
         <v>1518</v>
       </c>
-      <c r="F8" s="0" t="n">
-        <v>27.9166666666667</v>
-      </c>
-      <c r="G8" s="0" t="n">
-        <v>0</v>
+      <c r="F8" s="0">
+        <v>27.916666666666668</v>
+      </c>
+      <c r="G8" s="0">
+        <v>0.004995004995004995</v>
       </c>
       <c r="I8" s="0" t="s">
         <v>1518</v>
       </c>
-      <c r="J8" s="0" t="n">
-        <v>31.6666666666667</v>
-      </c>
-      <c r="K8" s="0" t="n">
-        <v>0</v>
+      <c r="J8" s="0">
+        <v>31.666666666666664</v>
+      </c>
+      <c r="K8" s="0">
+        <v>0.004995004995004995</v>
       </c>
       <c r="M8" s="0" t="s">
         <v>1518</v>
       </c>
-      <c r="N8" s="0" t="n">
-        <v>25.4166666666667</v>
-      </c>
-      <c r="O8" s="0" t="n">
-        <v>0</v>
+      <c r="N8" s="0">
+        <v>25.416666666666664</v>
+      </c>
+      <c r="O8" s="0">
+        <v>0.004995004995004995</v>
       </c>
       <c r="Q8" s="0" t="s">
         <v>1518</v>
       </c>
-      <c r="R8" s="0" t="n">
+      <c r="R8" s="0">
         <v>22.5</v>
       </c>
-      <c r="S8" s="0" t="n">
-        <v>0</v>
+      <c r="S8" s="0">
+        <v>0.004995004995004995</v>
       </c>
       <c r="U8" s="0" t="s">
         <v>1518</v>
       </c>
-      <c r="V8" s="0" t="n">
-        <v>15.8333333333333</v>
-      </c>
-      <c r="W8" s="0" t="n">
-        <v>0</v>
+      <c r="V8" s="0">
+        <v>15.833333333333332</v>
+      </c>
+      <c r="W8" s="0">
+        <v>0.004995004995004995</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
         <v>1519</v>
       </c>
-      <c r="B9" s="0" t="n">
+      <c r="B9" s="0">
         <v>77.5</v>
       </c>
-      <c r="C9" s="0" t="n">
-        <v>0</v>
+      <c r="C9" s="0">
+        <v>0.004995004995004995</v>
       </c>
       <c r="E9" s="0" t="s">
         <v>1519</v>
       </c>
-      <c r="F9" s="0" t="n">
+      <c r="F9" s="0">
         <v>76.25</v>
       </c>
-      <c r="G9" s="0" t="n">
-        <v>0</v>
+      <c r="G9" s="0">
+        <v>0.004995004995004995</v>
       </c>
       <c r="I9" s="0" t="s">
         <v>1519</v>
       </c>
-      <c r="J9" s="0" t="n">
-        <v>57.5</v>
-      </c>
-      <c r="K9" s="0" t="n">
-        <v>0</v>
+      <c r="J9" s="0">
+        <v>57.499999999999993</v>
+      </c>
+      <c r="K9" s="0">
+        <v>0.004995004995004995</v>
       </c>
       <c r="M9" s="0" t="s">
         <v>1519</v>
       </c>
-      <c r="N9" s="0" t="n">
-        <v>52.9166666666667</v>
-      </c>
-      <c r="O9" s="0" t="n">
-        <v>0</v>
+      <c r="N9" s="0">
+        <v>52.916666666666664</v>
+      </c>
+      <c r="O9" s="0">
+        <v>0.004995004995004995</v>
       </c>
       <c r="Q9" s="0" t="s">
         <v>1519</v>
       </c>
-      <c r="R9" s="0" t="n">
-        <v>39.5833333333333</v>
-      </c>
-      <c r="S9" s="0" t="n">
-        <v>0</v>
+      <c r="R9" s="0">
+        <v>39.583333333333329</v>
+      </c>
+      <c r="S9" s="0">
+        <v>0.004995004995004995</v>
       </c>
       <c r="U9" s="0" t="s">
         <v>1519</v>
       </c>
-      <c r="V9" s="0" t="n">
-        <v>28.3333333333333</v>
-      </c>
-      <c r="W9" s="0" t="n">
-        <v>0</v>
+      <c r="V9" s="0">
+        <v>28.333333333333332</v>
+      </c>
+      <c r="W9" s="0">
+        <v>0.004995004995004995</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
         <v>1520</v>
       </c>
-      <c r="B10" s="0" t="n">
-        <v>93.3333333333333</v>
-      </c>
-      <c r="C10" s="0" t="n">
-        <v>0</v>
+      <c r="B10" s="0">
+        <v>93.333333333333329</v>
+      </c>
+      <c r="C10" s="0">
+        <v>0.004995004995004995</v>
       </c>
       <c r="E10" s="0" t="s">
         <v>1520</v>
       </c>
-      <c r="F10" s="0" t="n">
+      <c r="F10" s="0">
         <v>86.25</v>
       </c>
-      <c r="G10" s="0" t="n">
-        <v>0</v>
+      <c r="G10" s="0">
+        <v>0.004995004995004995</v>
       </c>
       <c r="I10" s="0" t="s">
         <v>1520</v>
       </c>
-      <c r="J10" s="0" t="n">
-        <v>72.9166666666667</v>
-      </c>
-      <c r="K10" s="0" t="n">
-        <v>0</v>
+      <c r="J10" s="0">
+        <v>72.916666666666657</v>
+      </c>
+      <c r="K10" s="0">
+        <v>0.004995004995004995</v>
       </c>
       <c r="M10" s="0" t="s">
         <v>1520</v>
       </c>
-      <c r="N10" s="0" t="n">
-        <v>64.5833333333333</v>
-      </c>
-      <c r="O10" s="0" t="n">
-        <v>0</v>
+      <c r="N10" s="0">
+        <v>64.583333333333343</v>
+      </c>
+      <c r="O10" s="0">
+        <v>0.004995004995004995</v>
       </c>
       <c r="Q10" s="0" t="s">
         <v>1520</v>
       </c>
-      <c r="R10" s="0" t="n">
+      <c r="R10" s="0">
         <v>47.5</v>
       </c>
-      <c r="S10" s="0" t="n">
-        <v>0</v>
+      <c r="S10" s="0">
+        <v>0.004995004995004995</v>
       </c>
       <c r="U10" s="0" t="s">
         <v>1520</v>
       </c>
-      <c r="V10" s="0" t="n">
+      <c r="V10" s="0">
         <v>43.75</v>
       </c>
-      <c r="W10" s="0" t="n">
-        <v>0</v>
+      <c r="W10" s="0">
+        <v>0.004995004995004995</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
         <v>1521</v>
       </c>
-      <c r="B11" s="0" t="n">
+      <c r="B11" s="0">
         <v>11.25</v>
       </c>
-      <c r="C11" s="0" t="n">
-        <v>0</v>
+      <c r="C11" s="0">
+        <v>0.004995004995004995</v>
       </c>
       <c r="E11" s="0" t="s">
         <v>1521</v>
       </c>
-      <c r="F11" s="0" t="n">
-        <v>10.4166666666667</v>
-      </c>
-      <c r="G11" s="0" t="n">
-        <v>0</v>
+      <c r="F11" s="0">
+        <v>10.416666666666668</v>
+      </c>
+      <c r="G11" s="0">
+        <v>0.004995004995004995</v>
       </c>
       <c r="I11" s="0" t="s">
         <v>1521</v>
       </c>
-      <c r="J11" s="0" t="n">
-        <v>19.1666666666667</v>
-      </c>
-      <c r="K11" s="0" t="n">
-        <v>0</v>
+      <c r="J11" s="0">
+        <v>19.166666666666668</v>
+      </c>
+      <c r="K11" s="0">
+        <v>0.004995004995004995</v>
       </c>
       <c r="M11" s="0" t="s">
         <v>1521</v>
       </c>
-      <c r="N11" s="0" t="n">
-        <v>10.8333333333333</v>
-      </c>
-      <c r="O11" s="0" t="n">
-        <v>0</v>
+      <c r="N11" s="0">
+        <v>10.833333333333334</v>
+      </c>
+      <c r="O11" s="0">
+        <v>0.004995004995004995</v>
       </c>
       <c r="Q11" s="0" t="s">
         <v>1521</v>
       </c>
-      <c r="R11" s="0" t="n">
+      <c r="R11" s="0">
         <v>17.5</v>
       </c>
-      <c r="S11" s="0" t="n">
-        <v>0</v>
+      <c r="S11" s="0">
+        <v>0.004995004995004995</v>
       </c>
       <c r="U11" s="0" t="s">
         <v>1521</v>
       </c>
-      <c r="V11" s="0" t="n">
-        <v>2.91666666666667</v>
-      </c>
-      <c r="W11" s="0" t="n">
-        <v>2.69</v>
+      <c r="V11" s="0">
+        <v>2.9166666666666665</v>
+      </c>
+      <c r="W11" s="0">
+        <v>3.6413586413586412</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="0" t="s">
         <v>1522</v>
       </c>
-      <c r="B12" s="0" t="n">
-        <v>29.5833333333333</v>
-      </c>
-      <c r="C12" s="0" t="n">
-        <v>0</v>
+      <c r="B12" s="0">
+        <v>29.583333333333332</v>
+      </c>
+      <c r="C12" s="0">
+        <v>0.004995004995004995</v>
       </c>
       <c r="E12" s="0" t="s">
         <v>1522</v>
       </c>
-      <c r="F12" s="0" t="n">
+      <c r="F12" s="0">
         <v>25</v>
       </c>
-      <c r="G12" s="0" t="n">
-        <v>0</v>
+      <c r="G12" s="0">
+        <v>0.004995004995004995</v>
       </c>
       <c r="I12" s="0" t="s">
         <v>1522</v>
       </c>
-      <c r="J12" s="0" t="n">
-        <v>26.6666666666667</v>
-      </c>
-      <c r="K12" s="0" t="n">
-        <v>0</v>
+      <c r="J12" s="0">
+        <v>26.666666666666668</v>
+      </c>
+      <c r="K12" s="0">
+        <v>0.004995004995004995</v>
       </c>
       <c r="M12" s="0" t="s">
         <v>1522</v>
       </c>
-      <c r="N12" s="0" t="n">
+      <c r="N12" s="0">
         <v>22.5</v>
       </c>
-      <c r="O12" s="0" t="n">
-        <v>0</v>
+      <c r="O12" s="0">
+        <v>0.004995004995004995</v>
       </c>
       <c r="Q12" s="0" t="s">
         <v>1522</v>
       </c>
-      <c r="R12" s="0" t="n">
-        <v>29.1666666666667</v>
-      </c>
-      <c r="S12" s="0" t="n">
-        <v>0</v>
+      <c r="R12" s="0">
+        <v>29.166666666666668</v>
+      </c>
+      <c r="S12" s="0">
+        <v>0.004995004995004995</v>
       </c>
       <c r="U12" s="0" t="s">
         <v>1522</v>
       </c>
-      <c r="V12" s="0" t="n">
-        <v>16.6666666666667</v>
-      </c>
-      <c r="W12" s="0" t="n">
-        <v>0</v>
+      <c r="V12" s="0">
+        <v>16.666666666666664</v>
+      </c>
+      <c r="W12" s="0">
+        <v>0.004995004995004995</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="0" t="s">
         <v>1523</v>
       </c>
-      <c r="B13" s="0" t="n">
-        <v>87.0833333333333</v>
-      </c>
-      <c r="C13" s="0" t="n">
-        <v>0</v>
+      <c r="B13" s="0">
+        <v>87.083333333333329</v>
+      </c>
+      <c r="C13" s="0">
+        <v>0.004995004995004995</v>
       </c>
       <c r="E13" s="0" t="s">
         <v>1523</v>
       </c>
-      <c r="F13" s="0" t="n">
-        <v>84.1666666666667</v>
-      </c>
-      <c r="G13" s="0" t="n">
-        <v>0</v>
+      <c r="F13" s="0">
+        <v>84.166666666666672</v>
+      </c>
+      <c r="G13" s="0">
+        <v>0.004995004995004995</v>
       </c>
       <c r="I13" s="0" t="s">
         <v>1523</v>
       </c>
-      <c r="J13" s="0" t="n">
-        <v>70.4166666666667</v>
-      </c>
-      <c r="K13" s="0" t="n">
-        <v>0</v>
+      <c r="J13" s="0">
+        <v>70.416666666666672</v>
+      </c>
+      <c r="K13" s="0">
+        <v>0.004995004995004995</v>
       </c>
       <c r="M13" s="0" t="s">
         <v>1523</v>
       </c>
-      <c r="N13" s="0" t="n">
+      <c r="N13" s="0">
         <v>65</v>
       </c>
-      <c r="O13" s="0" t="n">
-        <v>0</v>
+      <c r="O13" s="0">
+        <v>0.004995004995004995</v>
       </c>
       <c r="Q13" s="0" t="s">
         <v>1523</v>
       </c>
-      <c r="R13" s="0" t="n">
-        <v>41.6666666666667</v>
-      </c>
-      <c r="S13" s="0" t="n">
-        <v>0</v>
+      <c r="R13" s="0">
+        <v>41.666666666666671</v>
+      </c>
+      <c r="S13" s="0">
+        <v>0.004995004995004995</v>
       </c>
       <c r="U13" s="0" t="s">
         <v>1523</v>
       </c>
-      <c r="V13" s="0" t="n">
-        <v>53.3333333333333</v>
-      </c>
-      <c r="W13" s="0" t="n">
-        <v>0</v>
+      <c r="V13" s="0">
+        <v>53.333333333333336</v>
+      </c>
+      <c r="W13" s="0">
+        <v>0.004995004995004995</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="0" t="s">
         <v>1524</v>
       </c>
-      <c r="B14" s="0" t="n">
+      <c r="B14" s="0">
         <v>95</v>
       </c>
-      <c r="C14" s="0" t="n">
-        <v>0</v>
+      <c r="C14" s="0">
+        <v>0.004995004995004995</v>
       </c>
       <c r="E14" s="0" t="s">
         <v>1524</v>
       </c>
-      <c r="F14" s="0" t="n">
+      <c r="F14" s="0">
         <v>92.5</v>
       </c>
-      <c r="G14" s="0" t="n">
-        <v>0</v>
+      <c r="G14" s="0">
+        <v>0.004995004995004995</v>
       </c>
       <c r="I14" s="0" t="s">
         <v>1524</v>
       </c>
-      <c r="J14" s="0" t="n">
-        <v>79.1666666666667</v>
-      </c>
-      <c r="K14" s="0" t="n">
-        <v>0</v>
+      <c r="J14" s="0">
+        <v>79.166666666666657</v>
+      </c>
+      <c r="K14" s="0">
+        <v>0.004995004995004995</v>
       </c>
       <c r="M14" s="0" t="s">
         <v>1524</v>
       </c>
-      <c r="N14" s="0" t="n">
+      <c r="N14" s="0">
         <v>71.25</v>
       </c>
-      <c r="O14" s="0" t="n">
-        <v>0</v>
+      <c r="O14" s="0">
+        <v>0.004995004995004995</v>
       </c>
       <c r="Q14" s="0" t="s">
         <v>1524</v>
       </c>
-      <c r="R14" s="0" t="n">
+      <c r="R14" s="0">
         <v>56.25</v>
       </c>
-      <c r="S14" s="0" t="n">
-        <v>0</v>
+      <c r="S14" s="0">
+        <v>0.004995004995004995</v>
       </c>
       <c r="U14" s="0" t="s">
         <v>1524</v>
       </c>
-      <c r="V14" s="0" t="n">
-        <v>64.5833333333333</v>
-      </c>
-      <c r="W14" s="0" t="n">
-        <v>0</v>
+      <c r="V14" s="0">
+        <v>64.583333333333343</v>
+      </c>
+      <c r="W14" s="0">
+        <v>0.004995004995004995</v>
       </c>
     </row>
   </sheetData>
@@ -22562,77 +22584,95 @@
   <dimension ref="A1:W14"/>
   <sheetFormatPr defaultColWidth="8.6953125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="10.99" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
-    <col min="2" max="2" width="20.57" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
-    <col min="3" max="3" width="22.86" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
-    <col min="5" max="5" width="10.99" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
-    <col min="6" max="6" width="20.57" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
-    <col min="7" max="7" width="22.86" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
-    <col min="9" max="9" width="10.99" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
-    <col min="10" max="10" width="20.57" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
-    <col min="11" max="11" width="22.86" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
-    <col min="13" max="13" width="10.99" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
-    <col min="14" max="14" width="20.57" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
-    <col min="15" max="15" width="22.86" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
-    <col min="17" max="17" width="10.99" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
-    <col min="18" max="18" width="20.57" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
-    <col min="19" max="19" width="22.86" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
-    <col min="21" max="21" width="10.99" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
-    <col min="22" max="22" width="20.57" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
-    <col min="23" max="23" width="22.86" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="1" max="1" width="11" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="2" max="2" width="20.5703125" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="3" max="3" width="22.85546875" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="5" max="5" width="11" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="6" max="6" width="20.5703125" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="7" max="7" width="22.85546875" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="9" max="9" width="11" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="10" max="10" width="20.5703125" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="11" max="11" width="22.85546875" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="13" max="13" width="11" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="14" max="14" width="20.5703125" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="15" max="15" width="22.85546875" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="17" max="17" width="11" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="18" max="18" width="20.5703125" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="19" max="19" width="22.85546875" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="21" max="21" width="11" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="22" max="22" width="20.5703125" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="23" max="23" width="22.85546875" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
         <v>1506</v>
       </c>
+      <c r="B1" s="0"/>
+      <c r="C1" s="0"/>
       <c r="E1" s="0" t="s">
         <v>1507</v>
       </c>
+      <c r="F1" s="0"/>
+      <c r="G1" s="0"/>
       <c r="I1" s="0" t="s">
         <v>1508</v>
       </c>
+      <c r="J1" s="0"/>
+      <c r="K1" s="0"/>
       <c r="M1" s="0" t="s">
         <v>1509</v>
       </c>
+      <c r="N1" s="0"/>
+      <c r="O1" s="0"/>
       <c r="Q1" s="0" t="s">
         <v>1510</v>
       </c>
+      <c r="R1" s="0"/>
+      <c r="S1" s="0"/>
       <c r="U1" s="0" t="s">
         <v>1511</v>
       </c>
+      <c r="V1" s="0"/>
+      <c r="W1" s="0"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="0"/>
       <c r="B2" s="0" t="s">
         <v>1512</v>
       </c>
       <c r="C2" s="0" t="s">
         <v>34</v>
       </c>
+      <c r="E2" s="0"/>
       <c r="F2" s="0" t="s">
         <v>1512</v>
       </c>
       <c r="G2" s="0" t="s">
         <v>34</v>
       </c>
+      <c r="I2" s="0"/>
       <c r="J2" s="0" t="s">
         <v>1512</v>
       </c>
       <c r="K2" s="0" t="s">
         <v>34</v>
       </c>
+      <c r="M2" s="0"/>
       <c r="N2" s="0" t="s">
         <v>1512</v>
       </c>
       <c r="O2" s="0" t="s">
         <v>34</v>
       </c>
+      <c r="Q2" s="0"/>
       <c r="R2" s="0" t="s">
         <v>1512</v>
       </c>
       <c r="S2" s="0" t="s">
         <v>34</v>
       </c>
+      <c r="U2" s="0"/>
       <c r="V2" s="0" t="s">
         <v>1512</v>
       </c>
@@ -22644,672 +22684,672 @@
       <c r="A3" s="0" t="s">
         <v>1525</v>
       </c>
-      <c r="B3" s="0" t="n">
-        <v>14.5833333333333</v>
-      </c>
-      <c r="C3" s="0" t="n">
-        <v>0</v>
+      <c r="B3" s="0">
+        <v>14.583333333333334</v>
+      </c>
+      <c r="C3" s="0">
+        <v>0.004995004995004995</v>
       </c>
       <c r="E3" s="0" t="s">
         <v>1525</v>
       </c>
-      <c r="F3" s="0" t="n">
+      <c r="F3" s="0">
         <v>11.25</v>
       </c>
-      <c r="G3" s="0" t="n">
-        <v>0</v>
+      <c r="G3" s="0">
+        <v>0.004995004995004995</v>
       </c>
       <c r="I3" s="0" t="s">
         <v>1525</v>
       </c>
-      <c r="J3" s="0" t="n">
-        <v>14.5833333333333</v>
-      </c>
-      <c r="K3" s="0" t="n">
-        <v>0</v>
+      <c r="J3" s="0">
+        <v>14.583333333333334</v>
+      </c>
+      <c r="K3" s="0">
+        <v>0.004995004995004995</v>
       </c>
       <c r="M3" s="0" t="s">
         <v>1525</v>
       </c>
-      <c r="N3" s="0" t="n">
-        <v>9.16666666666667</v>
-      </c>
-      <c r="O3" s="0" t="n">
-        <v>0</v>
+      <c r="N3" s="0">
+        <v>9.1666666666666661</v>
+      </c>
+      <c r="O3" s="0">
+        <v>0.004995004995004995</v>
       </c>
       <c r="Q3" s="0" t="s">
         <v>1525</v>
       </c>
-      <c r="R3" s="0" t="n">
-        <v>19.5833333333333</v>
-      </c>
-      <c r="S3" s="0" t="n">
-        <v>0</v>
+      <c r="R3" s="0">
+        <v>19.583333333333332</v>
+      </c>
+      <c r="S3" s="0">
+        <v>0.004995004995004995</v>
       </c>
       <c r="U3" s="0" t="s">
         <v>1525</v>
       </c>
-      <c r="V3" s="0" t="n">
-        <v>3.33333333333333</v>
-      </c>
-      <c r="W3" s="0" t="n">
-        <v>1.98</v>
+      <c r="V3" s="0">
+        <v>3.3333333333333335</v>
+      </c>
+      <c r="W3" s="0">
+        <v>2.7922077922077921</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
         <v>1526</v>
       </c>
-      <c r="B4" s="0" t="n">
-        <v>52.0833333333333</v>
-      </c>
-      <c r="C4" s="0" t="n">
-        <v>0</v>
+      <c r="B4" s="0">
+        <v>52.083333333333336</v>
+      </c>
+      <c r="C4" s="0">
+        <v>0.004995004995004995</v>
       </c>
       <c r="E4" s="0" t="s">
         <v>1526</v>
       </c>
-      <c r="F4" s="0" t="n">
+      <c r="F4" s="0">
         <v>30</v>
       </c>
-      <c r="G4" s="0" t="n">
-        <v>0</v>
+      <c r="G4" s="0">
+        <v>0.004995004995004995</v>
       </c>
       <c r="I4" s="0" t="s">
         <v>1526</v>
       </c>
-      <c r="J4" s="0" t="n">
-        <v>30.8333333333333</v>
-      </c>
-      <c r="K4" s="0" t="n">
-        <v>0</v>
+      <c r="J4" s="0">
+        <v>30.833333333333336</v>
+      </c>
+      <c r="K4" s="0">
+        <v>0.004995004995004995</v>
       </c>
       <c r="M4" s="0" t="s">
         <v>1526</v>
       </c>
-      <c r="N4" s="0" t="n">
+      <c r="N4" s="0">
         <v>30</v>
       </c>
-      <c r="O4" s="0" t="n">
-        <v>0</v>
+      <c r="O4" s="0">
+        <v>0.004995004995004995</v>
       </c>
       <c r="Q4" s="0" t="s">
         <v>1526</v>
       </c>
-      <c r="R4" s="0" t="n">
-        <v>36.6666666666667</v>
-      </c>
-      <c r="S4" s="0" t="n">
-        <v>0</v>
+      <c r="R4" s="0">
+        <v>36.666666666666664</v>
+      </c>
+      <c r="S4" s="0">
+        <v>0.004995004995004995</v>
       </c>
       <c r="U4" s="0" t="s">
         <v>1526</v>
       </c>
-      <c r="V4" s="0" t="n">
-        <v>13.75</v>
-      </c>
-      <c r="W4" s="0" t="n">
-        <v>0</v>
+      <c r="V4" s="0">
+        <v>13.750000000000002</v>
+      </c>
+      <c r="W4" s="0">
+        <v>0.004995004995004995</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
         <v>1527</v>
       </c>
-      <c r="B5" s="0" t="n">
-        <v>6.66666666666667</v>
-      </c>
-      <c r="C5" s="0" t="n">
-        <v>0.01</v>
+      <c r="B5" s="0">
+        <v>6.666666666666667</v>
+      </c>
+      <c r="C5" s="0">
+        <v>0.024975024975024976</v>
       </c>
       <c r="E5" s="0" t="s">
         <v>1527</v>
       </c>
-      <c r="F5" s="0" t="n">
-        <v>14.1666666666667</v>
-      </c>
-      <c r="G5" s="0" t="n">
-        <v>0</v>
+      <c r="F5" s="0">
+        <v>14.166666666666666</v>
+      </c>
+      <c r="G5" s="0">
+        <v>0.004995004995004995</v>
       </c>
       <c r="I5" s="0" t="s">
         <v>1527</v>
       </c>
-      <c r="J5" s="0" t="n">
-        <v>11.6666666666667</v>
-      </c>
-      <c r="K5" s="0" t="n">
-        <v>0</v>
+      <c r="J5" s="0">
+        <v>11.666666666666666</v>
+      </c>
+      <c r="K5" s="0">
+        <v>0.004995004995004995</v>
       </c>
       <c r="M5" s="0" t="s">
         <v>1527</v>
       </c>
-      <c r="N5" s="0" t="n">
-        <v>15.4166666666667</v>
-      </c>
-      <c r="O5" s="0" t="n">
-        <v>0</v>
+      <c r="N5" s="0">
+        <v>15.416666666666668</v>
+      </c>
+      <c r="O5" s="0">
+        <v>0.004995004995004995</v>
       </c>
       <c r="Q5" s="0" t="s">
         <v>1527</v>
       </c>
-      <c r="R5" s="0" t="n">
+      <c r="R5" s="0">
         <v>6.25</v>
       </c>
-      <c r="S5" s="0" t="n">
-        <v>0.02</v>
+      <c r="S5" s="0">
+        <v>0.059940059940059937</v>
       </c>
       <c r="U5" s="0" t="s">
         <v>1527</v>
       </c>
-      <c r="V5" s="0" t="n">
-        <v>3.33333333333333</v>
-      </c>
-      <c r="W5" s="0" t="n">
-        <v>2.38</v>
+      <c r="V5" s="0">
+        <v>3.3333333333333335</v>
+      </c>
+      <c r="W5" s="0">
+        <v>3.291708291708292</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
         <v>1528</v>
       </c>
-      <c r="B6" s="0" t="n">
+      <c r="B6" s="0">
         <v>73.75</v>
       </c>
-      <c r="C6" s="0" t="n">
-        <v>0</v>
+      <c r="C6" s="0">
+        <v>0.004995004995004995</v>
       </c>
       <c r="E6" s="0" t="s">
         <v>1528</v>
       </c>
-      <c r="F6" s="0" t="n">
-        <v>44.1666666666667</v>
-      </c>
-      <c r="G6" s="0" t="n">
-        <v>0</v>
+      <c r="F6" s="0">
+        <v>44.166666666666664</v>
+      </c>
+      <c r="G6" s="0">
+        <v>0.004995004995004995</v>
       </c>
       <c r="I6" s="0" t="s">
         <v>1528</v>
       </c>
-      <c r="J6" s="0" t="n">
-        <v>48.3333333333333</v>
-      </c>
-      <c r="K6" s="0" t="n">
-        <v>0</v>
+      <c r="J6" s="0">
+        <v>48.333333333333336</v>
+      </c>
+      <c r="K6" s="0">
+        <v>0.004995004995004995</v>
       </c>
       <c r="M6" s="0" t="s">
         <v>1528</v>
       </c>
-      <c r="N6" s="0" t="n">
+      <c r="N6" s="0">
         <v>35</v>
       </c>
-      <c r="O6" s="0" t="n">
-        <v>0</v>
+      <c r="O6" s="0">
+        <v>0.004995004995004995</v>
       </c>
       <c r="Q6" s="0" t="s">
         <v>1528</v>
       </c>
-      <c r="R6" s="0" t="n">
+      <c r="R6" s="0">
         <v>40</v>
       </c>
-      <c r="S6" s="0" t="n">
-        <v>0</v>
+      <c r="S6" s="0">
+        <v>0.004995004995004995</v>
       </c>
       <c r="U6" s="0" t="s">
         <v>1528</v>
       </c>
-      <c r="V6" s="0" t="n">
+      <c r="V6" s="0">
         <v>20</v>
       </c>
-      <c r="W6" s="0" t="n">
-        <v>0</v>
+      <c r="W6" s="0">
+        <v>0.004995004995004995</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
         <v>1529</v>
       </c>
-      <c r="B7" s="0" t="n">
-        <v>9.16666666666667</v>
-      </c>
-      <c r="C7" s="0" t="n">
-        <v>0</v>
+      <c r="B7" s="0">
+        <v>9.1666666666666661</v>
+      </c>
+      <c r="C7" s="0">
+        <v>0.004995004995004995</v>
       </c>
       <c r="E7" s="0" t="s">
         <v>1529</v>
       </c>
-      <c r="F7" s="0" t="n">
+      <c r="F7" s="0">
         <v>5</v>
       </c>
-      <c r="G7" s="0" t="n">
-        <v>0.215</v>
+      <c r="G7" s="0">
+        <v>0.37462537462537465</v>
       </c>
       <c r="I7" s="0" t="s">
         <v>1529</v>
       </c>
-      <c r="J7" s="0" t="n">
-        <v>14.5833333333333</v>
-      </c>
-      <c r="K7" s="0" t="n">
-        <v>0</v>
+      <c r="J7" s="0">
+        <v>14.583333333333334</v>
+      </c>
+      <c r="K7" s="0">
+        <v>0.004995004995004995</v>
       </c>
       <c r="M7" s="0" t="s">
         <v>1529</v>
       </c>
-      <c r="N7" s="0" t="n">
+      <c r="N7" s="0">
         <v>11.25</v>
       </c>
-      <c r="O7" s="0" t="n">
-        <v>0</v>
+      <c r="O7" s="0">
+        <v>0.004995004995004995</v>
       </c>
       <c r="Q7" s="0" t="s">
         <v>1529</v>
       </c>
-      <c r="R7" s="0" t="n">
+      <c r="R7" s="0">
         <v>18.75</v>
       </c>
-      <c r="S7" s="0" t="n">
-        <v>0</v>
+      <c r="S7" s="0">
+        <v>0.004995004995004995</v>
       </c>
       <c r="U7" s="0" t="s">
         <v>1529</v>
       </c>
-      <c r="V7" s="0" t="n">
-        <v>5.41666666666667</v>
-      </c>
-      <c r="W7" s="0" t="n">
-        <v>0.055</v>
+      <c r="V7" s="0">
+        <v>5.416666666666667</v>
+      </c>
+      <c r="W7" s="0">
+        <v>0.14485514485514486</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
         <v>1530</v>
       </c>
-      <c r="B8" s="0" t="n">
-        <v>52.0833333333333</v>
-      </c>
-      <c r="C8" s="0" t="n">
-        <v>0</v>
+      <c r="B8" s="0">
+        <v>52.083333333333336</v>
+      </c>
+      <c r="C8" s="0">
+        <v>0.004995004995004995</v>
       </c>
       <c r="E8" s="0" t="s">
         <v>1530</v>
       </c>
-      <c r="F8" s="0" t="n">
+      <c r="F8" s="0">
         <v>37.5</v>
       </c>
-      <c r="G8" s="0" t="n">
-        <v>0</v>
+      <c r="G8" s="0">
+        <v>0.004995004995004995</v>
       </c>
       <c r="I8" s="0" t="s">
         <v>1530</v>
       </c>
-      <c r="J8" s="0" t="n">
+      <c r="J8" s="0">
         <v>38.75</v>
       </c>
-      <c r="K8" s="0" t="n">
-        <v>0</v>
+      <c r="K8" s="0">
+        <v>0.004995004995004995</v>
       </c>
       <c r="M8" s="0" t="s">
         <v>1530</v>
       </c>
-      <c r="N8" s="0" t="n">
-        <v>30.4166666666667</v>
-      </c>
-      <c r="O8" s="0" t="n">
-        <v>0</v>
+      <c r="N8" s="0">
+        <v>30.416666666666664</v>
+      </c>
+      <c r="O8" s="0">
+        <v>0.004995004995004995</v>
       </c>
       <c r="Q8" s="0" t="s">
         <v>1530</v>
       </c>
-      <c r="R8" s="0" t="n">
-        <v>38.3333333333333</v>
-      </c>
-      <c r="S8" s="0" t="n">
-        <v>0</v>
+      <c r="R8" s="0">
+        <v>38.333333333333336</v>
+      </c>
+      <c r="S8" s="0">
+        <v>0.004995004995004995</v>
       </c>
       <c r="U8" s="0" t="s">
         <v>1530</v>
       </c>
-      <c r="V8" s="0" t="n">
-        <v>25.4166666666667</v>
-      </c>
-      <c r="W8" s="0" t="n">
-        <v>0</v>
+      <c r="V8" s="0">
+        <v>25.416666666666664</v>
+      </c>
+      <c r="W8" s="0">
+        <v>0.004995004995004995</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
         <v>1531</v>
       </c>
-      <c r="B9" s="0" t="n">
-        <v>79.1666666666667</v>
-      </c>
-      <c r="C9" s="0" t="n">
-        <v>0</v>
+      <c r="B9" s="0">
+        <v>79.166666666666657</v>
+      </c>
+      <c r="C9" s="0">
+        <v>0.004995004995004995</v>
       </c>
       <c r="E9" s="0" t="s">
         <v>1531</v>
       </c>
-      <c r="F9" s="0" t="n">
-        <v>72.0833333333333</v>
-      </c>
-      <c r="G9" s="0" t="n">
-        <v>0</v>
+      <c r="F9" s="0">
+        <v>72.083333333333329</v>
+      </c>
+      <c r="G9" s="0">
+        <v>0.004995004995004995</v>
       </c>
       <c r="I9" s="0" t="s">
         <v>1531</v>
       </c>
-      <c r="J9" s="0" t="n">
-        <v>57.5</v>
-      </c>
-      <c r="K9" s="0" t="n">
-        <v>0</v>
+      <c r="J9" s="0">
+        <v>57.499999999999993</v>
+      </c>
+      <c r="K9" s="0">
+        <v>0.004995004995004995</v>
       </c>
       <c r="M9" s="0" t="s">
         <v>1531</v>
       </c>
-      <c r="N9" s="0" t="n">
+      <c r="N9" s="0">
         <v>52.5</v>
       </c>
-      <c r="O9" s="0" t="n">
-        <v>0</v>
+      <c r="O9" s="0">
+        <v>0.004995004995004995</v>
       </c>
       <c r="Q9" s="0" t="s">
         <v>1531</v>
       </c>
-      <c r="R9" s="0" t="n">
+      <c r="R9" s="0">
         <v>37.5</v>
       </c>
-      <c r="S9" s="0" t="n">
-        <v>0</v>
+      <c r="S9" s="0">
+        <v>0.004995004995004995</v>
       </c>
       <c r="U9" s="0" t="s">
         <v>1531</v>
       </c>
-      <c r="V9" s="0" t="n">
-        <v>20.4166666666667</v>
-      </c>
-      <c r="W9" s="0" t="n">
-        <v>0</v>
+      <c r="V9" s="0">
+        <v>20.416666666666668</v>
+      </c>
+      <c r="W9" s="0">
+        <v>0.004995004995004995</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
         <v>1532</v>
       </c>
-      <c r="B10" s="0" t="n">
-        <v>79.1666666666667</v>
-      </c>
-      <c r="C10" s="0" t="n">
-        <v>0</v>
+      <c r="B10" s="0">
+        <v>79.166666666666657</v>
+      </c>
+      <c r="C10" s="0">
+        <v>0.004995004995004995</v>
       </c>
       <c r="E10" s="0" t="s">
         <v>1532</v>
       </c>
-      <c r="F10" s="0" t="n">
-        <v>64.1666666666667</v>
-      </c>
-      <c r="G10" s="0" t="n">
-        <v>0</v>
+      <c r="F10" s="0">
+        <v>64.166666666666672</v>
+      </c>
+      <c r="G10" s="0">
+        <v>0.004995004995004995</v>
       </c>
       <c r="I10" s="0" t="s">
         <v>1532</v>
       </c>
-      <c r="J10" s="0" t="n">
-        <v>52.0833333333333</v>
-      </c>
-      <c r="K10" s="0" t="n">
-        <v>0</v>
+      <c r="J10" s="0">
+        <v>52.083333333333336</v>
+      </c>
+      <c r="K10" s="0">
+        <v>0.004995004995004995</v>
       </c>
       <c r="M10" s="0" t="s">
         <v>1532</v>
       </c>
-      <c r="N10" s="0" t="n">
-        <v>44.5833333333333</v>
-      </c>
-      <c r="O10" s="0" t="n">
-        <v>0</v>
+      <c r="N10" s="0">
+        <v>44.583333333333336</v>
+      </c>
+      <c r="O10" s="0">
+        <v>0.004995004995004995</v>
       </c>
       <c r="Q10" s="0" t="s">
         <v>1532</v>
       </c>
-      <c r="R10" s="0" t="n">
-        <v>45.8333333333333</v>
-      </c>
-      <c r="S10" s="0" t="n">
-        <v>0</v>
+      <c r="R10" s="0">
+        <v>45.833333333333329</v>
+      </c>
+      <c r="S10" s="0">
+        <v>0.004995004995004995</v>
       </c>
       <c r="U10" s="0" t="s">
         <v>1532</v>
       </c>
-      <c r="V10" s="0" t="n">
-        <v>25.8333333333333</v>
-      </c>
-      <c r="W10" s="0" t="n">
-        <v>0</v>
+      <c r="V10" s="0">
+        <v>25.833333333333336</v>
+      </c>
+      <c r="W10" s="0">
+        <v>0.004995004995004995</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
         <v>1533</v>
       </c>
-      <c r="B11" s="0" t="n">
-        <v>9.16666666666667</v>
-      </c>
-      <c r="C11" s="0" t="n">
-        <v>0</v>
+      <c r="B11" s="0">
+        <v>9.1666666666666661</v>
+      </c>
+      <c r="C11" s="0">
+        <v>0.004995004995004995</v>
       </c>
       <c r="E11" s="0" t="s">
         <v>1533</v>
       </c>
-      <c r="F11" s="0" t="n">
-        <v>5.83333333333333</v>
-      </c>
-      <c r="G11" s="0" t="n">
-        <v>0.05</v>
+      <c r="F11" s="0">
+        <v>5.833333333333333</v>
+      </c>
+      <c r="G11" s="0">
+        <v>0.13986013986013987</v>
       </c>
       <c r="I11" s="0" t="s">
         <v>1533</v>
       </c>
-      <c r="J11" s="0" t="n">
-        <v>12.9166666666667</v>
-      </c>
-      <c r="K11" s="0" t="n">
-        <v>0</v>
+      <c r="J11" s="0">
+        <v>12.916666666666668</v>
+      </c>
+      <c r="K11" s="0">
+        <v>0.004995004995004995</v>
       </c>
       <c r="M11" s="0" t="s">
         <v>1533</v>
       </c>
-      <c r="N11" s="0" t="n">
+      <c r="N11" s="0">
         <v>11.25</v>
       </c>
-      <c r="O11" s="0" t="n">
-        <v>0</v>
+      <c r="O11" s="0">
+        <v>0.004995004995004995</v>
       </c>
       <c r="Q11" s="0" t="s">
         <v>1533</v>
       </c>
-      <c r="R11" s="0" t="n">
-        <v>17.0833333333333</v>
-      </c>
-      <c r="S11" s="0" t="n">
-        <v>0</v>
+      <c r="R11" s="0">
+        <v>17.083333333333332</v>
+      </c>
+      <c r="S11" s="0">
+        <v>0.004995004995004995</v>
       </c>
       <c r="U11" s="0" t="s">
         <v>1533</v>
       </c>
-      <c r="V11" s="0" t="n">
-        <v>5.41666666666667</v>
-      </c>
-      <c r="W11" s="0" t="n">
-        <v>0.1</v>
+      <c r="V11" s="0">
+        <v>5.416666666666667</v>
+      </c>
+      <c r="W11" s="0">
+        <v>0.1848151848151848</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="0" t="s">
         <v>1534</v>
       </c>
-      <c r="B12" s="0" t="n">
-        <v>55.8333333333333</v>
-      </c>
-      <c r="C12" s="0" t="n">
-        <v>0</v>
+      <c r="B12" s="0">
+        <v>55.833333333333336</v>
+      </c>
+      <c r="C12" s="0">
+        <v>0.004995004995004995</v>
       </c>
       <c r="E12" s="0" t="s">
         <v>1534</v>
       </c>
-      <c r="F12" s="0" t="n">
-        <v>40.4166666666667</v>
-      </c>
-      <c r="G12" s="0" t="n">
-        <v>0</v>
+      <c r="F12" s="0">
+        <v>40.416666666666664</v>
+      </c>
+      <c r="G12" s="0">
+        <v>0.004995004995004995</v>
       </c>
       <c r="I12" s="0" t="s">
         <v>1534</v>
       </c>
-      <c r="J12" s="0" t="n">
+      <c r="J12" s="0">
         <v>41.25</v>
       </c>
-      <c r="K12" s="0" t="n">
-        <v>0</v>
+      <c r="K12" s="0">
+        <v>0.004995004995004995</v>
       </c>
       <c r="M12" s="0" t="s">
         <v>1534</v>
       </c>
-      <c r="N12" s="0" t="n">
+      <c r="N12" s="0">
         <v>35</v>
       </c>
-      <c r="O12" s="0" t="n">
-        <v>0</v>
+      <c r="O12" s="0">
+        <v>0.004995004995004995</v>
       </c>
       <c r="Q12" s="0" t="s">
         <v>1534</v>
       </c>
-      <c r="R12" s="0" t="n">
-        <v>41.6666666666667</v>
-      </c>
-      <c r="S12" s="0" t="n">
-        <v>0</v>
+      <c r="R12" s="0">
+        <v>41.666666666666671</v>
+      </c>
+      <c r="S12" s="0">
+        <v>0.004995004995004995</v>
       </c>
       <c r="U12" s="0" t="s">
         <v>1534</v>
       </c>
-      <c r="V12" s="0" t="n">
-        <v>25.4166666666667</v>
-      </c>
-      <c r="W12" s="0" t="n">
-        <v>0</v>
+      <c r="V12" s="0">
+        <v>25.416666666666664</v>
+      </c>
+      <c r="W12" s="0">
+        <v>0.004995004995004995</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="0" t="s">
         <v>1535</v>
       </c>
-      <c r="B13" s="0" t="n">
-        <v>77.9166666666667</v>
-      </c>
-      <c r="C13" s="0" t="n">
-        <v>0</v>
+      <c r="B13" s="0">
+        <v>77.916666666666672</v>
+      </c>
+      <c r="C13" s="0">
+        <v>0.004995004995004995</v>
       </c>
       <c r="E13" s="0" t="s">
         <v>1535</v>
       </c>
-      <c r="F13" s="0" t="n">
-        <v>76.6666666666667</v>
-      </c>
-      <c r="G13" s="0" t="n">
-        <v>0</v>
+      <c r="F13" s="0">
+        <v>76.666666666666672</v>
+      </c>
+      <c r="G13" s="0">
+        <v>0.004995004995004995</v>
       </c>
       <c r="I13" s="0" t="s">
         <v>1535</v>
       </c>
-      <c r="J13" s="0" t="n">
-        <v>56.6666666666667</v>
-      </c>
-      <c r="K13" s="0" t="n">
-        <v>0</v>
+      <c r="J13" s="0">
+        <v>56.666666666666664</v>
+      </c>
+      <c r="K13" s="0">
+        <v>0.004995004995004995</v>
       </c>
       <c r="M13" s="0" t="s">
         <v>1535</v>
       </c>
-      <c r="N13" s="0" t="n">
+      <c r="N13" s="0">
         <v>50</v>
       </c>
-      <c r="O13" s="0" t="n">
-        <v>0</v>
+      <c r="O13" s="0">
+        <v>0.004995004995004995</v>
       </c>
       <c r="Q13" s="0" t="s">
         <v>1535</v>
       </c>
-      <c r="R13" s="0" t="n">
-        <v>27.0833333333333</v>
-      </c>
-      <c r="S13" s="0" t="n">
-        <v>0</v>
+      <c r="R13" s="0">
+        <v>27.083333333333332</v>
+      </c>
+      <c r="S13" s="0">
+        <v>0.004995004995004995</v>
       </c>
       <c r="U13" s="0" t="s">
         <v>1535</v>
       </c>
-      <c r="V13" s="0" t="n">
-        <v>9.16666666666667</v>
-      </c>
-      <c r="W13" s="0" t="n">
-        <v>0</v>
+      <c r="V13" s="0">
+        <v>9.1666666666666661</v>
+      </c>
+      <c r="W13" s="0">
+        <v>0.004995004995004995</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="0" t="s">
         <v>1536</v>
       </c>
-      <c r="B14" s="0" t="n">
-        <v>86.6666666666667</v>
-      </c>
-      <c r="C14" s="0" t="n">
-        <v>0</v>
+      <c r="B14" s="0">
+        <v>86.666666666666672</v>
+      </c>
+      <c r="C14" s="0">
+        <v>0.004995004995004995</v>
       </c>
       <c r="E14" s="0" t="s">
         <v>1536</v>
       </c>
-      <c r="F14" s="0" t="n">
-        <v>74.1666666666667</v>
-      </c>
-      <c r="G14" s="0" t="n">
-        <v>0</v>
+      <c r="F14" s="0">
+        <v>74.166666666666672</v>
+      </c>
+      <c r="G14" s="0">
+        <v>0.004995004995004995</v>
       </c>
       <c r="I14" s="0" t="s">
         <v>1536</v>
       </c>
-      <c r="J14" s="0" t="n">
-        <v>61.25</v>
-      </c>
-      <c r="K14" s="0" t="n">
-        <v>0</v>
+      <c r="J14" s="0">
+        <v>61.250000000000007</v>
+      </c>
+      <c r="K14" s="0">
+        <v>0.004995004995004995</v>
       </c>
       <c r="M14" s="0" t="s">
         <v>1536</v>
       </c>
-      <c r="N14" s="0" t="n">
-        <v>55.4166666666667</v>
-      </c>
-      <c r="O14" s="0" t="n">
-        <v>0</v>
+      <c r="N14" s="0">
+        <v>55.416666666666671</v>
+      </c>
+      <c r="O14" s="0">
+        <v>0.004995004995004995</v>
       </c>
       <c r="Q14" s="0" t="s">
         <v>1536</v>
       </c>
-      <c r="R14" s="0" t="n">
+      <c r="R14" s="0">
         <v>48.75</v>
       </c>
-      <c r="S14" s="0" t="n">
-        <v>0</v>
+      <c r="S14" s="0">
+        <v>0.004995004995004995</v>
       </c>
       <c r="U14" s="0" t="s">
         <v>1536</v>
       </c>
-      <c r="V14" s="0" t="n">
-        <v>48.3333333333333</v>
-      </c>
-      <c r="W14" s="0" t="n">
-        <v>0</v>
+      <c r="V14" s="0">
+        <v>48.333333333333336</v>
+      </c>
+      <c r="W14" s="0">
+        <v>0.004995004995004995</v>
       </c>
     </row>
   </sheetData>
@@ -23529,77 +23569,95 @@
   <dimension ref="A1:W14"/>
   <sheetFormatPr defaultColWidth="8.6953125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="14.57" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
-    <col min="2" max="2" width="20.57" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
-    <col min="3" max="3" width="22.86" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
-    <col min="5" max="5" width="14.57" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
-    <col min="6" max="6" width="20.57" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
-    <col min="7" max="7" width="22.86" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
-    <col min="9" max="9" width="14.57" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
-    <col min="10" max="10" width="20.57" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
-    <col min="11" max="11" width="22.86" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
-    <col min="13" max="13" width="14.57" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
-    <col min="14" max="14" width="20.57" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
-    <col min="15" max="15" width="22.86" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
-    <col min="17" max="17" width="14.57" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
-    <col min="18" max="18" width="20.57" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
-    <col min="19" max="19" width="22.86" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
-    <col min="21" max="21" width="14.57" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
-    <col min="22" max="22" width="20.57" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
-    <col min="23" max="23" width="22.86" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="1" max="1" width="14.5703125" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="2" max="2" width="20.5703125" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="3" max="3" width="22.85546875" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="5" max="5" width="14.5703125" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="6" max="6" width="20.5703125" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="7" max="7" width="22.85546875" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="9" max="9" width="14.5703125" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="10" max="10" width="20.5703125" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="11" max="11" width="22.85546875" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="13" max="13" width="14.5703125" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="14" max="14" width="20.5703125" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="15" max="15" width="22.85546875" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="17" max="17" width="14.5703125" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="18" max="18" width="20.5703125" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="19" max="19" width="22.85546875" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="21" max="21" width="14.5703125" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="22" max="22" width="20.5703125" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="23" max="23" width="22.85546875" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
         <v>1506</v>
       </c>
+      <c r="B1" s="0"/>
+      <c r="C1" s="0"/>
       <c r="E1" s="0" t="s">
         <v>1507</v>
       </c>
+      <c r="F1" s="0"/>
+      <c r="G1" s="0"/>
       <c r="I1" s="0" t="s">
         <v>1508</v>
       </c>
+      <c r="J1" s="0"/>
+      <c r="K1" s="0"/>
       <c r="M1" s="0" t="s">
         <v>1509</v>
       </c>
+      <c r="N1" s="0"/>
+      <c r="O1" s="0"/>
       <c r="Q1" s="0" t="s">
         <v>1510</v>
       </c>
+      <c r="R1" s="0"/>
+      <c r="S1" s="0"/>
       <c r="U1" s="0" t="s">
         <v>1511</v>
       </c>
+      <c r="V1" s="0"/>
+      <c r="W1" s="0"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="0"/>
       <c r="B2" s="0" t="s">
         <v>1512</v>
       </c>
       <c r="C2" s="0" t="s">
         <v>34</v>
       </c>
+      <c r="E2" s="0"/>
       <c r="F2" s="0" t="s">
         <v>1512</v>
       </c>
       <c r="G2" s="0" t="s">
         <v>34</v>
       </c>
+      <c r="I2" s="0"/>
       <c r="J2" s="0" t="s">
         <v>1512</v>
       </c>
       <c r="K2" s="0" t="s">
         <v>34</v>
       </c>
+      <c r="M2" s="0"/>
       <c r="N2" s="0" t="s">
         <v>1512</v>
       </c>
       <c r="O2" s="0" t="s">
         <v>34</v>
       </c>
+      <c r="Q2" s="0"/>
       <c r="R2" s="0" t="s">
         <v>1512</v>
       </c>
       <c r="S2" s="0" t="s">
         <v>34</v>
       </c>
+      <c r="U2" s="0"/>
       <c r="V2" s="0" t="s">
         <v>1512</v>
       </c>
@@ -23611,672 +23669,672 @@
       <c r="A3" s="0" t="s">
         <v>1537</v>
       </c>
-      <c r="B3" s="0" t="n">
+      <c r="B3" s="0">
         <v>8.75</v>
       </c>
-      <c r="C3" s="0" t="n">
-        <v>0</v>
+      <c r="C3" s="0">
+        <v>0.004995004995004995</v>
       </c>
       <c r="E3" s="0" t="s">
         <v>1537</v>
       </c>
-      <c r="F3" s="0" t="n">
-        <v>9.16666666666667</v>
-      </c>
-      <c r="G3" s="0" t="n">
-        <v>0</v>
+      <c r="F3" s="0">
+        <v>9.1666666666666661</v>
+      </c>
+      <c r="G3" s="0">
+        <v>0.004995004995004995</v>
       </c>
       <c r="I3" s="0" t="s">
         <v>1537</v>
       </c>
-      <c r="J3" s="0" t="n">
-        <v>15.4166666666667</v>
-      </c>
-      <c r="K3" s="0" t="n">
-        <v>0</v>
+      <c r="J3" s="0">
+        <v>15.416666666666668</v>
+      </c>
+      <c r="K3" s="0">
+        <v>0.004995004995004995</v>
       </c>
       <c r="M3" s="0" t="s">
         <v>1537</v>
       </c>
-      <c r="N3" s="0" t="n">
-        <v>12.9166666666667</v>
-      </c>
-      <c r="O3" s="0" t="n">
-        <v>0</v>
+      <c r="N3" s="0">
+        <v>12.916666666666668</v>
+      </c>
+      <c r="O3" s="0">
+        <v>0.004995004995004995</v>
       </c>
       <c r="Q3" s="0" t="s">
         <v>1537</v>
       </c>
-      <c r="R3" s="0" t="n">
-        <v>10.4166666666667</v>
-      </c>
-      <c r="S3" s="0" t="n">
-        <v>0</v>
+      <c r="R3" s="0">
+        <v>10.416666666666668</v>
+      </c>
+      <c r="S3" s="0">
+        <v>0.004995004995004995</v>
       </c>
       <c r="U3" s="0" t="s">
         <v>1537</v>
       </c>
-      <c r="V3" s="0" t="n">
-        <v>2.08333333333333</v>
-      </c>
-      <c r="W3" s="0" t="n">
-        <v>3.745</v>
+      <c r="V3" s="0">
+        <v>2.083333333333333</v>
+      </c>
+      <c r="W3" s="0">
+        <v>4.5854145854145854</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
         <v>1538</v>
       </c>
-      <c r="B4" s="0" t="n">
-        <v>38.3333333333333</v>
-      </c>
-      <c r="C4" s="0" t="n">
-        <v>0</v>
+      <c r="B4" s="0">
+        <v>38.333333333333336</v>
+      </c>
+      <c r="C4" s="0">
+        <v>0.004995004995004995</v>
       </c>
       <c r="E4" s="0" t="s">
         <v>1538</v>
       </c>
-      <c r="F4" s="0" t="n">
-        <v>24.5833333333333</v>
-      </c>
-      <c r="G4" s="0" t="n">
-        <v>0</v>
+      <c r="F4" s="0">
+        <v>24.583333333333332</v>
+      </c>
+      <c r="G4" s="0">
+        <v>0.004995004995004995</v>
       </c>
       <c r="I4" s="0" t="s">
         <v>1538</v>
       </c>
-      <c r="J4" s="0" t="n">
-        <v>28.75</v>
-      </c>
-      <c r="K4" s="0" t="n">
-        <v>0</v>
+      <c r="J4" s="0">
+        <v>28.749999999999997</v>
+      </c>
+      <c r="K4" s="0">
+        <v>0.004995004995004995</v>
       </c>
       <c r="M4" s="0" t="s">
         <v>1538</v>
       </c>
-      <c r="N4" s="0" t="n">
+      <c r="N4" s="0">
         <v>16.25</v>
       </c>
-      <c r="O4" s="0" t="n">
-        <v>0</v>
+      <c r="O4" s="0">
+        <v>0.004995004995004995</v>
       </c>
       <c r="Q4" s="0" t="s">
         <v>1538</v>
       </c>
-      <c r="R4" s="0" t="n">
-        <v>38.3333333333333</v>
-      </c>
-      <c r="S4" s="0" t="n">
-        <v>0</v>
+      <c r="R4" s="0">
+        <v>38.333333333333336</v>
+      </c>
+      <c r="S4" s="0">
+        <v>0.004995004995004995</v>
       </c>
       <c r="U4" s="0" t="s">
         <v>1538</v>
       </c>
-      <c r="V4" s="0" t="n">
+      <c r="V4" s="0">
         <v>15</v>
       </c>
-      <c r="W4" s="0" t="n">
-        <v>0</v>
+      <c r="W4" s="0">
+        <v>0.004995004995004995</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
         <v>1539</v>
       </c>
-      <c r="B5" s="0" t="n">
-        <v>85.8333333333333</v>
-      </c>
-      <c r="C5" s="0" t="n">
-        <v>0</v>
+      <c r="B5" s="0">
+        <v>85.833333333333329</v>
+      </c>
+      <c r="C5" s="0">
+        <v>0.004995004995004995</v>
       </c>
       <c r="E5" s="0" t="s">
         <v>1539</v>
       </c>
-      <c r="F5" s="0" t="n">
-        <v>62.9166666666667</v>
-      </c>
-      <c r="G5" s="0" t="n">
-        <v>0</v>
+      <c r="F5" s="0">
+        <v>62.916666666666664</v>
+      </c>
+      <c r="G5" s="0">
+        <v>0.004995004995004995</v>
       </c>
       <c r="I5" s="0" t="s">
         <v>1539</v>
       </c>
-      <c r="J5" s="0" t="n">
-        <v>57.9166666666667</v>
-      </c>
-      <c r="K5" s="0" t="n">
-        <v>0</v>
+      <c r="J5" s="0">
+        <v>57.916666666666672</v>
+      </c>
+      <c r="K5" s="0">
+        <v>0.004995004995004995</v>
       </c>
       <c r="M5" s="0" t="s">
         <v>1539</v>
       </c>
-      <c r="N5" s="0" t="n">
+      <c r="N5" s="0">
         <v>47.5</v>
       </c>
-      <c r="O5" s="0" t="n">
-        <v>0</v>
+      <c r="O5" s="0">
+        <v>0.004995004995004995</v>
       </c>
       <c r="Q5" s="0" t="s">
         <v>1539</v>
       </c>
-      <c r="R5" s="0" t="n">
-        <v>44.1666666666667</v>
-      </c>
-      <c r="S5" s="0" t="n">
-        <v>0</v>
+      <c r="R5" s="0">
+        <v>44.166666666666664</v>
+      </c>
+      <c r="S5" s="0">
+        <v>0.004995004995004995</v>
       </c>
       <c r="U5" s="0" t="s">
         <v>1539</v>
       </c>
-      <c r="V5" s="0" t="n">
-        <v>22.0833333333333</v>
-      </c>
-      <c r="W5" s="0" t="n">
-        <v>0</v>
+      <c r="V5" s="0">
+        <v>22.083333333333332</v>
+      </c>
+      <c r="W5" s="0">
+        <v>0.004995004995004995</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
         <v>1540</v>
       </c>
-      <c r="B6" s="0" t="n">
-        <v>85.4166666666667</v>
-      </c>
-      <c r="C6" s="0" t="n">
-        <v>0</v>
+      <c r="B6" s="0">
+        <v>85.416666666666657</v>
+      </c>
+      <c r="C6" s="0">
+        <v>0.004995004995004995</v>
       </c>
       <c r="E6" s="0" t="s">
         <v>1540</v>
       </c>
-      <c r="F6" s="0" t="n">
-        <v>71.6666666666667</v>
-      </c>
-      <c r="G6" s="0" t="n">
-        <v>0</v>
+      <c r="F6" s="0">
+        <v>71.666666666666672</v>
+      </c>
+      <c r="G6" s="0">
+        <v>0.004995004995004995</v>
       </c>
       <c r="I6" s="0" t="s">
         <v>1540</v>
       </c>
-      <c r="J6" s="0" t="n">
-        <v>62.0833333333333</v>
-      </c>
-      <c r="K6" s="0" t="n">
-        <v>0</v>
+      <c r="J6" s="0">
+        <v>62.083333333333336</v>
+      </c>
+      <c r="K6" s="0">
+        <v>0.004995004995004995</v>
       </c>
       <c r="M6" s="0" t="s">
         <v>1540</v>
       </c>
-      <c r="N6" s="0" t="n">
+      <c r="N6" s="0">
         <v>52.5</v>
       </c>
-      <c r="O6" s="0" t="n">
-        <v>0</v>
+      <c r="O6" s="0">
+        <v>0.004995004995004995</v>
       </c>
       <c r="Q6" s="0" t="s">
         <v>1540</v>
       </c>
-      <c r="R6" s="0" t="n">
-        <v>47.9166666666667</v>
-      </c>
-      <c r="S6" s="0" t="n">
-        <v>0</v>
+      <c r="R6" s="0">
+        <v>47.916666666666671</v>
+      </c>
+      <c r="S6" s="0">
+        <v>0.004995004995004995</v>
       </c>
       <c r="U6" s="0" t="s">
         <v>1540</v>
       </c>
-      <c r="V6" s="0" t="n">
+      <c r="V6" s="0">
         <v>30</v>
       </c>
-      <c r="W6" s="0" t="n">
-        <v>0</v>
+      <c r="W6" s="0">
+        <v>0.004995004995004995</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
         <v>1541</v>
       </c>
-      <c r="B7" s="0" t="n">
-        <v>2.91666666666667</v>
-      </c>
-      <c r="C7" s="0" t="n">
-        <v>2.54</v>
+      <c r="B7" s="0">
+        <v>2.9166666666666665</v>
+      </c>
+      <c r="C7" s="0">
+        <v>3.3016983016983015</v>
       </c>
       <c r="E7" s="0" t="s">
         <v>1541</v>
       </c>
-      <c r="F7" s="0" t="n">
-        <v>9.58333333333333</v>
-      </c>
-      <c r="G7" s="0" t="n">
-        <v>0</v>
+      <c r="F7" s="0">
+        <v>9.5833333333333339</v>
+      </c>
+      <c r="G7" s="0">
+        <v>0.004995004995004995</v>
       </c>
       <c r="I7" s="0" t="s">
         <v>1541</v>
       </c>
-      <c r="J7" s="0" t="n">
+      <c r="J7" s="0">
         <v>7.5</v>
       </c>
-      <c r="K7" s="0" t="n">
-        <v>0</v>
+      <c r="K7" s="0">
+        <v>0.014985014985014984</v>
       </c>
       <c r="M7" s="0" t="s">
         <v>1541</v>
       </c>
-      <c r="N7" s="0" t="n">
-        <v>10.4166666666667</v>
-      </c>
-      <c r="O7" s="0" t="n">
-        <v>0</v>
+      <c r="N7" s="0">
+        <v>10.416666666666668</v>
+      </c>
+      <c r="O7" s="0">
+        <v>0.004995004995004995</v>
       </c>
       <c r="Q7" s="0" t="s">
         <v>1541</v>
       </c>
-      <c r="R7" s="0" t="n">
-        <v>11.6666666666667</v>
-      </c>
-      <c r="S7" s="0" t="n">
-        <v>0</v>
+      <c r="R7" s="0">
+        <v>11.666666666666666</v>
+      </c>
+      <c r="S7" s="0">
+        <v>0.004995004995004995</v>
       </c>
       <c r="U7" s="0" t="s">
         <v>1541</v>
       </c>
-      <c r="V7" s="0" t="n">
+      <c r="V7" s="0">
         <v>5</v>
       </c>
-      <c r="W7" s="0" t="n">
-        <v>0.15</v>
+      <c r="W7" s="0">
+        <v>0.3046953046953047</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
         <v>1542</v>
       </c>
-      <c r="B8" s="0" t="n">
-        <v>16.6666666666667</v>
-      </c>
-      <c r="C8" s="0" t="n">
-        <v>0</v>
+      <c r="B8" s="0">
+        <v>16.666666666666664</v>
+      </c>
+      <c r="C8" s="0">
+        <v>0.004995004995004995</v>
       </c>
       <c r="E8" s="0" t="s">
         <v>1542</v>
       </c>
-      <c r="F8" s="0" t="n">
-        <v>24.1666666666667</v>
-      </c>
-      <c r="G8" s="0" t="n">
-        <v>0</v>
+      <c r="F8" s="0">
+        <v>24.166666666666668</v>
+      </c>
+      <c r="G8" s="0">
+        <v>0.004995004995004995</v>
       </c>
       <c r="I8" s="0" t="s">
         <v>1542</v>
       </c>
-      <c r="J8" s="0" t="n">
-        <v>23.3333333333333</v>
-      </c>
-      <c r="K8" s="0" t="n">
-        <v>0</v>
+      <c r="J8" s="0">
+        <v>23.333333333333332</v>
+      </c>
+      <c r="K8" s="0">
+        <v>0.004995004995004995</v>
       </c>
       <c r="M8" s="0" t="s">
         <v>1542</v>
       </c>
-      <c r="N8" s="0" t="n">
-        <v>16.6666666666667</v>
-      </c>
-      <c r="O8" s="0" t="n">
-        <v>0</v>
+      <c r="N8" s="0">
+        <v>16.666666666666664</v>
+      </c>
+      <c r="O8" s="0">
+        <v>0.004995004995004995</v>
       </c>
       <c r="Q8" s="0" t="s">
         <v>1542</v>
       </c>
-      <c r="R8" s="0" t="n">
+      <c r="R8" s="0">
         <v>25</v>
       </c>
-      <c r="S8" s="0" t="n">
-        <v>0</v>
+      <c r="S8" s="0">
+        <v>0.004995004995004995</v>
       </c>
       <c r="U8" s="0" t="s">
         <v>1542</v>
       </c>
-      <c r="V8" s="0" t="n">
-        <v>6.66666666666667</v>
-      </c>
-      <c r="W8" s="0" t="n">
-        <v>0</v>
+      <c r="V8" s="0">
+        <v>6.666666666666667</v>
+      </c>
+      <c r="W8" s="0">
+        <v>0.00999000999000999</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
         <v>1543</v>
       </c>
-      <c r="B9" s="0" t="n">
-        <v>53.3333333333333</v>
-      </c>
-      <c r="C9" s="0" t="n">
-        <v>0</v>
+      <c r="B9" s="0">
+        <v>53.333333333333336</v>
+      </c>
+      <c r="C9" s="0">
+        <v>0.004995004995004995</v>
       </c>
       <c r="E9" s="0" t="s">
         <v>1543</v>
       </c>
-      <c r="F9" s="0" t="n">
+      <c r="F9" s="0">
         <v>52.5</v>
       </c>
-      <c r="G9" s="0" t="n">
-        <v>0</v>
+      <c r="G9" s="0">
+        <v>0.004995004995004995</v>
       </c>
       <c r="I9" s="0" t="s">
         <v>1543</v>
       </c>
-      <c r="J9" s="0" t="n">
-        <v>45.4166666666667</v>
-      </c>
-      <c r="K9" s="0" t="n">
-        <v>0</v>
+      <c r="J9" s="0">
+        <v>45.416666666666664</v>
+      </c>
+      <c r="K9" s="0">
+        <v>0.004995004995004995</v>
       </c>
       <c r="M9" s="0" t="s">
         <v>1543</v>
       </c>
-      <c r="N9" s="0" t="n">
-        <v>39.1666666666667</v>
-      </c>
-      <c r="O9" s="0" t="n">
-        <v>0</v>
+      <c r="N9" s="0">
+        <v>39.166666666666664</v>
+      </c>
+      <c r="O9" s="0">
+        <v>0.004995004995004995</v>
       </c>
       <c r="Q9" s="0" t="s">
         <v>1543</v>
       </c>
-      <c r="R9" s="0" t="n">
-        <v>28.3333333333333</v>
-      </c>
-      <c r="S9" s="0" t="n">
-        <v>0</v>
+      <c r="R9" s="0">
+        <v>28.333333333333332</v>
+      </c>
+      <c r="S9" s="0">
+        <v>0.004995004995004995</v>
       </c>
       <c r="U9" s="0" t="s">
         <v>1543</v>
       </c>
-      <c r="V9" s="0" t="n">
-        <v>14.5833333333333</v>
-      </c>
-      <c r="W9" s="0" t="n">
-        <v>0</v>
+      <c r="V9" s="0">
+        <v>14.583333333333334</v>
+      </c>
+      <c r="W9" s="0">
+        <v>0.004995004995004995</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
         <v>1544</v>
       </c>
-      <c r="B10" s="0" t="n">
-        <v>54.1666666666667</v>
-      </c>
-      <c r="C10" s="0" t="n">
-        <v>0</v>
+      <c r="B10" s="0">
+        <v>54.166666666666664</v>
+      </c>
+      <c r="C10" s="0">
+        <v>0.004995004995004995</v>
       </c>
       <c r="E10" s="0" t="s">
         <v>1544</v>
       </c>
-      <c r="F10" s="0" t="n">
-        <v>55</v>
-      </c>
-      <c r="G10" s="0" t="n">
-        <v>0</v>
+      <c r="F10" s="0">
+        <v>55.000000000000007</v>
+      </c>
+      <c r="G10" s="0">
+        <v>0.004995004995004995</v>
       </c>
       <c r="I10" s="0" t="s">
         <v>1544</v>
       </c>
-      <c r="J10" s="0" t="n">
-        <v>44.1666666666667</v>
-      </c>
-      <c r="K10" s="0" t="n">
-        <v>0</v>
+      <c r="J10" s="0">
+        <v>44.166666666666664</v>
+      </c>
+      <c r="K10" s="0">
+        <v>0.004995004995004995</v>
       </c>
       <c r="M10" s="0" t="s">
         <v>1544</v>
       </c>
-      <c r="N10" s="0" t="n">
-        <v>44.5833333333333</v>
-      </c>
-      <c r="O10" s="0" t="n">
-        <v>0</v>
+      <c r="N10" s="0">
+        <v>44.583333333333336</v>
+      </c>
+      <c r="O10" s="0">
+        <v>0.004995004995004995</v>
       </c>
       <c r="Q10" s="0" t="s">
         <v>1544</v>
       </c>
-      <c r="R10" s="0" t="n">
-        <v>27.0833333333333</v>
-      </c>
-      <c r="S10" s="0" t="n">
-        <v>0</v>
+      <c r="R10" s="0">
+        <v>27.083333333333332</v>
+      </c>
+      <c r="S10" s="0">
+        <v>0.004995004995004995</v>
       </c>
       <c r="U10" s="0" t="s">
         <v>1544</v>
       </c>
-      <c r="V10" s="0" t="n">
-        <v>20.8333333333333</v>
-      </c>
-      <c r="W10" s="0" t="n">
-        <v>0</v>
+      <c r="V10" s="0">
+        <v>20.833333333333336</v>
+      </c>
+      <c r="W10" s="0">
+        <v>0.004995004995004995</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
         <v>1545</v>
       </c>
-      <c r="B11" s="0" t="n">
+      <c r="B11" s="0">
         <v>12.5</v>
       </c>
-      <c r="C11" s="0" t="n">
-        <v>0</v>
+      <c r="C11" s="0">
+        <v>0.004995004995004995</v>
       </c>
       <c r="E11" s="0" t="s">
         <v>1545</v>
       </c>
-      <c r="F11" s="0" t="n">
-        <v>7.91666666666667</v>
-      </c>
-      <c r="G11" s="0" t="n">
-        <v>0</v>
+      <c r="F11" s="0">
+        <v>7.9166666666666661</v>
+      </c>
+      <c r="G11" s="0">
+        <v>0.004995004995004995</v>
       </c>
       <c r="I11" s="0" t="s">
         <v>1545</v>
       </c>
-      <c r="J11" s="0" t="n">
-        <v>15.8333333333333</v>
-      </c>
-      <c r="K11" s="0" t="n">
-        <v>0</v>
+      <c r="J11" s="0">
+        <v>15.833333333333332</v>
+      </c>
+      <c r="K11" s="0">
+        <v>0.004995004995004995</v>
       </c>
       <c r="M11" s="0" t="s">
         <v>1545</v>
       </c>
-      <c r="N11" s="0" t="n">
-        <v>10.8333333333333</v>
-      </c>
-      <c r="O11" s="0" t="n">
-        <v>0</v>
+      <c r="N11" s="0">
+        <v>10.833333333333334</v>
+      </c>
+      <c r="O11" s="0">
+        <v>0.004995004995004995</v>
       </c>
       <c r="Q11" s="0" t="s">
         <v>1545</v>
       </c>
-      <c r="R11" s="0" t="n">
+      <c r="R11" s="0">
         <v>15</v>
       </c>
-      <c r="S11" s="0" t="n">
-        <v>0</v>
+      <c r="S11" s="0">
+        <v>0.004995004995004995</v>
       </c>
       <c r="U11" s="0" t="s">
         <v>1545</v>
       </c>
-      <c r="V11" s="0" t="n">
-        <v>2.91666666666667</v>
-      </c>
-      <c r="W11" s="0" t="n">
-        <v>2.175</v>
+      <c r="V11" s="0">
+        <v>2.9166666666666665</v>
+      </c>
+      <c r="W11" s="0">
+        <v>3.016983016983017</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="0" t="s">
         <v>1546</v>
       </c>
-      <c r="B12" s="0" t="n">
-        <v>29.5833333333333</v>
-      </c>
-      <c r="C12" s="0" t="n">
-        <v>0</v>
+      <c r="B12" s="0">
+        <v>29.583333333333332</v>
+      </c>
+      <c r="C12" s="0">
+        <v>0.004995004995004995</v>
       </c>
       <c r="E12" s="0" t="s">
         <v>1546</v>
       </c>
-      <c r="F12" s="0" t="n">
+      <c r="F12" s="0">
         <v>20</v>
       </c>
-      <c r="G12" s="0" t="n">
-        <v>0</v>
+      <c r="G12" s="0">
+        <v>0.004995004995004995</v>
       </c>
       <c r="I12" s="0" t="s">
         <v>1546</v>
       </c>
-      <c r="J12" s="0" t="n">
-        <v>23.3333333333333</v>
-      </c>
-      <c r="K12" s="0" t="n">
-        <v>0</v>
+      <c r="J12" s="0">
+        <v>23.333333333333332</v>
+      </c>
+      <c r="K12" s="0">
+        <v>0.004995004995004995</v>
       </c>
       <c r="M12" s="0" t="s">
         <v>1546</v>
       </c>
-      <c r="N12" s="0" t="n">
+      <c r="N12" s="0">
         <v>16.25</v>
       </c>
-      <c r="O12" s="0" t="n">
-        <v>0</v>
+      <c r="O12" s="0">
+        <v>0.004995004995004995</v>
       </c>
       <c r="Q12" s="0" t="s">
         <v>1546</v>
       </c>
-      <c r="R12" s="0" t="n">
-        <v>31.6666666666667</v>
-      </c>
-      <c r="S12" s="0" t="n">
-        <v>0</v>
+      <c r="R12" s="0">
+        <v>31.666666666666664</v>
+      </c>
+      <c r="S12" s="0">
+        <v>0.004995004995004995</v>
       </c>
       <c r="U12" s="0" t="s">
         <v>1546</v>
       </c>
-      <c r="V12" s="0" t="n">
-        <v>7.08333333333333</v>
-      </c>
-      <c r="W12" s="0" t="n">
-        <v>0.01</v>
+      <c r="V12" s="0">
+        <v>7.083333333333333</v>
+      </c>
+      <c r="W12" s="0">
+        <v>0.034965034965034968</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="0" t="s">
         <v>1547</v>
       </c>
-      <c r="B13" s="0" t="n">
-        <v>60.4166666666667</v>
-      </c>
-      <c r="C13" s="0" t="n">
-        <v>0</v>
+      <c r="B13" s="0">
+        <v>60.416666666666664</v>
+      </c>
+      <c r="C13" s="0">
+        <v>0.004995004995004995</v>
       </c>
       <c r="E13" s="0" t="s">
         <v>1547</v>
       </c>
-      <c r="F13" s="0" t="n">
-        <v>63.3333333333333</v>
-      </c>
-      <c r="G13" s="0" t="n">
-        <v>0</v>
+      <c r="F13" s="0">
+        <v>63.333333333333329</v>
+      </c>
+      <c r="G13" s="0">
+        <v>0.004995004995004995</v>
       </c>
       <c r="I13" s="0" t="s">
         <v>1547</v>
       </c>
-      <c r="J13" s="0" t="n">
-        <v>55.8333333333333</v>
-      </c>
-      <c r="K13" s="0" t="n">
-        <v>0</v>
+      <c r="J13" s="0">
+        <v>55.833333333333336</v>
+      </c>
+      <c r="K13" s="0">
+        <v>0.004995004995004995</v>
       </c>
       <c r="M13" s="0" t="s">
         <v>1547</v>
       </c>
-      <c r="N13" s="0" t="n">
-        <v>39.1666666666667</v>
-      </c>
-      <c r="O13" s="0" t="n">
-        <v>0</v>
+      <c r="N13" s="0">
+        <v>39.166666666666664</v>
+      </c>
+      <c r="O13" s="0">
+        <v>0.004995004995004995</v>
       </c>
       <c r="Q13" s="0" t="s">
         <v>1547</v>
       </c>
-      <c r="R13" s="0" t="n">
-        <v>21.6666666666667</v>
-      </c>
-      <c r="S13" s="0" t="n">
-        <v>0</v>
+      <c r="R13" s="0">
+        <v>21.666666666666668</v>
+      </c>
+      <c r="S13" s="0">
+        <v>0.004995004995004995</v>
       </c>
       <c r="U13" s="0" t="s">
         <v>1547</v>
       </c>
-      <c r="V13" s="0" t="n">
-        <v>27.5</v>
-      </c>
-      <c r="W13" s="0" t="n">
-        <v>0</v>
+      <c r="V13" s="0">
+        <v>27.500000000000004</v>
+      </c>
+      <c r="W13" s="0">
+        <v>0.004995004995004995</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="0" t="s">
         <v>1548</v>
       </c>
-      <c r="B14" s="0" t="n">
-        <v>64.1666666666667</v>
-      </c>
-      <c r="C14" s="0" t="n">
-        <v>0</v>
+      <c r="B14" s="0">
+        <v>64.166666666666672</v>
+      </c>
+      <c r="C14" s="0">
+        <v>0.004995004995004995</v>
       </c>
       <c r="E14" s="0" t="s">
         <v>1548</v>
       </c>
-      <c r="F14" s="0" t="n">
+      <c r="F14" s="0">
         <v>70</v>
       </c>
-      <c r="G14" s="0" t="n">
-        <v>0</v>
+      <c r="G14" s="0">
+        <v>0.004995004995004995</v>
       </c>
       <c r="I14" s="0" t="s">
         <v>1548</v>
       </c>
-      <c r="J14" s="0" t="n">
-        <v>60.4166666666667</v>
-      </c>
-      <c r="K14" s="0" t="n">
-        <v>0</v>
+      <c r="J14" s="0">
+        <v>60.416666666666664</v>
+      </c>
+      <c r="K14" s="0">
+        <v>0.004995004995004995</v>
       </c>
       <c r="M14" s="0" t="s">
         <v>1548</v>
       </c>
-      <c r="N14" s="0" t="n">
-        <v>41.6666666666667</v>
-      </c>
-      <c r="O14" s="0" t="n">
-        <v>0</v>
+      <c r="N14" s="0">
+        <v>41.666666666666671</v>
+      </c>
+      <c r="O14" s="0">
+        <v>0.004995004995004995</v>
       </c>
       <c r="Q14" s="0" t="s">
         <v>1548</v>
       </c>
-      <c r="R14" s="0" t="n">
+      <c r="R14" s="0">
         <v>25</v>
       </c>
-      <c r="S14" s="0" t="n">
-        <v>0</v>
+      <c r="S14" s="0">
+        <v>0.004995004995004995</v>
       </c>
       <c r="U14" s="0" t="s">
         <v>1548</v>
       </c>
-      <c r="V14" s="0" t="n">
-        <v>29.5833333333333</v>
-      </c>
-      <c r="W14" s="0" t="n">
-        <v>0</v>
+      <c r="V14" s="0">
+        <v>29.583333333333332</v>
+      </c>
+      <c r="W14" s="0">
+        <v>0.004995004995004995</v>
       </c>
     </row>
   </sheetData>
@@ -24298,77 +24356,95 @@
   <dimension ref="A1:W10"/>
   <sheetFormatPr defaultColWidth="8.6953125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="14.86" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
-    <col min="2" max="2" width="20.57" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
-    <col min="3" max="3" width="22.86" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
-    <col min="5" max="5" width="14.86" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
-    <col min="6" max="6" width="20.57" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
-    <col min="7" max="7" width="22.86" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
-    <col min="9" max="9" width="14.86" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
-    <col min="10" max="10" width="20.57" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
-    <col min="11" max="11" width="22.86" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
-    <col min="13" max="13" width="14.86" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
-    <col min="14" max="14" width="20.57" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
-    <col min="15" max="15" width="22.86" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
-    <col min="17" max="17" width="14.86" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
-    <col min="18" max="18" width="20.57" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
-    <col min="19" max="19" width="22.86" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
-    <col min="21" max="21" width="14.86" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
-    <col min="22" max="22" width="20.57" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
-    <col min="23" max="23" width="22.86" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="1" max="1" width="14.85546875" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="2" max="2" width="20.5703125" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="3" max="3" width="22.85546875" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="5" max="5" width="14.85546875" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="6" max="6" width="20.5703125" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="7" max="7" width="22.85546875" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="9" max="9" width="14.85546875" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="10" max="10" width="20.5703125" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="11" max="11" width="22.85546875" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="13" max="13" width="14.85546875" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="14" max="14" width="20.5703125" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="15" max="15" width="22.85546875" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="17" max="17" width="14.85546875" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="18" max="18" width="20.5703125" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="19" max="19" width="22.85546875" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="21" max="21" width="14.85546875" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="22" max="22" width="20.5703125" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="23" max="23" width="22.85546875" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
         <v>1506</v>
       </c>
+      <c r="B1" s="0"/>
+      <c r="C1" s="0"/>
       <c r="E1" s="0" t="s">
         <v>1507</v>
       </c>
+      <c r="F1" s="0"/>
+      <c r="G1" s="0"/>
       <c r="I1" s="0" t="s">
         <v>1508</v>
       </c>
+      <c r="J1" s="0"/>
+      <c r="K1" s="0"/>
       <c r="M1" s="0" t="s">
         <v>1509</v>
       </c>
+      <c r="N1" s="0"/>
+      <c r="O1" s="0"/>
       <c r="Q1" s="0" t="s">
         <v>1510</v>
       </c>
+      <c r="R1" s="0"/>
+      <c r="S1" s="0"/>
       <c r="U1" s="0" t="s">
         <v>1511</v>
       </c>
+      <c r="V1" s="0"/>
+      <c r="W1" s="0"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="0"/>
       <c r="B2" s="0" t="s">
         <v>1512</v>
       </c>
       <c r="C2" s="0" t="s">
         <v>34</v>
       </c>
+      <c r="E2" s="0"/>
       <c r="F2" s="0" t="s">
         <v>1512</v>
       </c>
       <c r="G2" s="0" t="s">
         <v>34</v>
       </c>
+      <c r="I2" s="0"/>
       <c r="J2" s="0" t="s">
         <v>1512</v>
       </c>
       <c r="K2" s="0" t="s">
         <v>34</v>
       </c>
+      <c r="M2" s="0"/>
       <c r="N2" s="0" t="s">
         <v>1512</v>
       </c>
       <c r="O2" s="0" t="s">
         <v>34</v>
       </c>
+      <c r="Q2" s="0"/>
       <c r="R2" s="0" t="s">
         <v>1512</v>
       </c>
       <c r="S2" s="0" t="s">
         <v>34</v>
       </c>
+      <c r="U2" s="0"/>
       <c r="V2" s="0" t="s">
         <v>1512</v>
       </c>
@@ -24380,448 +24456,448 @@
       <c r="A3" s="0" t="s">
         <v>1549</v>
       </c>
-      <c r="B3" s="0" t="n">
+      <c r="B3" s="0">
         <v>10</v>
       </c>
-      <c r="C3" s="0" t="n">
-        <v>0</v>
+      <c r="C3" s="0">
+        <v>0.004995004995004995</v>
       </c>
       <c r="E3" s="0" t="s">
         <v>1549</v>
       </c>
-      <c r="F3" s="0" t="n">
-        <v>6.66666666666667</v>
-      </c>
-      <c r="G3" s="0" t="n">
-        <v>0.005</v>
+      <c r="F3" s="0">
+        <v>6.666666666666667</v>
+      </c>
+      <c r="G3" s="0">
+        <v>0.024975024975024976</v>
       </c>
       <c r="I3" s="0" t="s">
         <v>1549</v>
       </c>
-      <c r="J3" s="0" t="n">
-        <v>12.0833333333333</v>
-      </c>
-      <c r="K3" s="0" t="n">
-        <v>0</v>
+      <c r="J3" s="0">
+        <v>12.083333333333334</v>
+      </c>
+      <c r="K3" s="0">
+        <v>0.004995004995004995</v>
       </c>
       <c r="M3" s="0" t="s">
         <v>1549</v>
       </c>
-      <c r="N3" s="0" t="n">
-        <v>9.58333333333333</v>
-      </c>
-      <c r="O3" s="0" t="n">
-        <v>0</v>
+      <c r="N3" s="0">
+        <v>9.5833333333333339</v>
+      </c>
+      <c r="O3" s="0">
+        <v>0.004995004995004995</v>
       </c>
       <c r="Q3" s="0" t="s">
         <v>1549</v>
       </c>
-      <c r="R3" s="0" t="n">
-        <v>14.5833333333333</v>
-      </c>
-      <c r="S3" s="0" t="n">
-        <v>0</v>
+      <c r="R3" s="0">
+        <v>14.583333333333334</v>
+      </c>
+      <c r="S3" s="0">
+        <v>0.004995004995004995</v>
       </c>
       <c r="U3" s="0" t="s">
         <v>1549</v>
       </c>
-      <c r="V3" s="0" t="n">
-        <v>4.16666666666667</v>
-      </c>
-      <c r="W3" s="0" t="n">
-        <v>0.65</v>
+      <c r="V3" s="0">
+        <v>4.1666666666666661</v>
+      </c>
+      <c r="W3" s="0">
+        <v>1.2137862137862139</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
         <v>1550</v>
       </c>
-      <c r="B4" s="0" t="n">
-        <v>30.8333333333333</v>
-      </c>
-      <c r="C4" s="0" t="n">
-        <v>0</v>
+      <c r="B4" s="0">
+        <v>30.833333333333336</v>
+      </c>
+      <c r="C4" s="0">
+        <v>0.004995004995004995</v>
       </c>
       <c r="E4" s="0" t="s">
         <v>1550</v>
       </c>
-      <c r="F4" s="0" t="n">
-        <v>22.9166666666667</v>
-      </c>
-      <c r="G4" s="0" t="n">
-        <v>0</v>
+      <c r="F4" s="0">
+        <v>22.916666666666664</v>
+      </c>
+      <c r="G4" s="0">
+        <v>0.004995004995004995</v>
       </c>
       <c r="I4" s="0" t="s">
         <v>1550</v>
       </c>
-      <c r="J4" s="0" t="n">
-        <v>24.5833333333333</v>
-      </c>
-      <c r="K4" s="0" t="n">
-        <v>0</v>
+      <c r="J4" s="0">
+        <v>24.583333333333332</v>
+      </c>
+      <c r="K4" s="0">
+        <v>0.004995004995004995</v>
       </c>
       <c r="M4" s="0" t="s">
         <v>1550</v>
       </c>
-      <c r="N4" s="0" t="n">
-        <v>19.5833333333333</v>
-      </c>
-      <c r="O4" s="0" t="n">
-        <v>0</v>
+      <c r="N4" s="0">
+        <v>19.583333333333332</v>
+      </c>
+      <c r="O4" s="0">
+        <v>0.004995004995004995</v>
       </c>
       <c r="Q4" s="0" t="s">
         <v>1550</v>
       </c>
-      <c r="R4" s="0" t="n">
-        <v>29.1666666666667</v>
-      </c>
-      <c r="S4" s="0" t="n">
-        <v>0</v>
+      <c r="R4" s="0">
+        <v>29.166666666666668</v>
+      </c>
+      <c r="S4" s="0">
+        <v>0.004995004995004995</v>
       </c>
       <c r="U4" s="0" t="s">
         <v>1550</v>
       </c>
-      <c r="V4" s="0" t="n">
-        <v>7.08333333333333</v>
-      </c>
-      <c r="W4" s="0" t="n">
-        <v>0</v>
+      <c r="V4" s="0">
+        <v>7.083333333333333</v>
+      </c>
+      <c r="W4" s="0">
+        <v>0.014985014985014984</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
         <v>1551</v>
       </c>
-      <c r="B5" s="0" t="n">
-        <v>77.0833333333333</v>
-      </c>
-      <c r="C5" s="0" t="n">
-        <v>0</v>
+      <c r="B5" s="0">
+        <v>77.083333333333343</v>
+      </c>
+      <c r="C5" s="0">
+        <v>0.004995004995004995</v>
       </c>
       <c r="E5" s="0" t="s">
         <v>1551</v>
       </c>
-      <c r="F5" s="0" t="n">
+      <c r="F5" s="0">
         <v>46.25</v>
       </c>
-      <c r="G5" s="0" t="n">
-        <v>0</v>
+      <c r="G5" s="0">
+        <v>0.004995004995004995</v>
       </c>
       <c r="I5" s="0" t="s">
         <v>1551</v>
       </c>
-      <c r="J5" s="0" t="n">
-        <v>55.4166666666667</v>
-      </c>
-      <c r="K5" s="0" t="n">
-        <v>0</v>
+      <c r="J5" s="0">
+        <v>55.416666666666671</v>
+      </c>
+      <c r="K5" s="0">
+        <v>0.004995004995004995</v>
       </c>
       <c r="M5" s="0" t="s">
         <v>1551</v>
       </c>
-      <c r="N5" s="0" t="n">
+      <c r="N5" s="0">
         <v>36.25</v>
       </c>
-      <c r="O5" s="0" t="n">
-        <v>0</v>
+      <c r="O5" s="0">
+        <v>0.004995004995004995</v>
       </c>
       <c r="Q5" s="0" t="s">
         <v>1551</v>
       </c>
-      <c r="R5" s="0" t="n">
-        <v>46.6666666666667</v>
-      </c>
-      <c r="S5" s="0" t="n">
-        <v>0</v>
+      <c r="R5" s="0">
+        <v>46.666666666666664</v>
+      </c>
+      <c r="S5" s="0">
+        <v>0.004995004995004995</v>
       </c>
       <c r="U5" s="0" t="s">
         <v>1551</v>
       </c>
-      <c r="V5" s="0" t="n">
-        <v>11.6666666666667</v>
-      </c>
-      <c r="W5" s="0" t="n">
-        <v>0</v>
+      <c r="V5" s="0">
+        <v>11.666666666666666</v>
+      </c>
+      <c r="W5" s="0">
+        <v>0.004995004995004995</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
         <v>1552</v>
       </c>
-      <c r="B6" s="0" t="n">
-        <v>82.0833333333333</v>
-      </c>
-      <c r="C6" s="0" t="n">
-        <v>0</v>
+      <c r="B6" s="0">
+        <v>82.083333333333329</v>
+      </c>
+      <c r="C6" s="0">
+        <v>0.004995004995004995</v>
       </c>
       <c r="E6" s="0" t="s">
         <v>1552</v>
       </c>
-      <c r="F6" s="0" t="n">
-        <v>57.0833333333333</v>
-      </c>
-      <c r="G6" s="0" t="n">
-        <v>0</v>
+      <c r="F6" s="0">
+        <v>57.083333333333329</v>
+      </c>
+      <c r="G6" s="0">
+        <v>0.004995004995004995</v>
       </c>
       <c r="I6" s="0" t="s">
         <v>1552</v>
       </c>
-      <c r="J6" s="0" t="n">
-        <v>62.9166666666667</v>
-      </c>
-      <c r="K6" s="0" t="n">
-        <v>0</v>
+      <c r="J6" s="0">
+        <v>62.916666666666664</v>
+      </c>
+      <c r="K6" s="0">
+        <v>0.004995004995004995</v>
       </c>
       <c r="M6" s="0" t="s">
         <v>1552</v>
       </c>
-      <c r="N6" s="0" t="n">
-        <v>45.8333333333333</v>
-      </c>
-      <c r="O6" s="0" t="n">
-        <v>0</v>
+      <c r="N6" s="0">
+        <v>45.833333333333329</v>
+      </c>
+      <c r="O6" s="0">
+        <v>0.004995004995004995</v>
       </c>
       <c r="Q6" s="0" t="s">
         <v>1552</v>
       </c>
-      <c r="R6" s="0" t="n">
+      <c r="R6" s="0">
         <v>47.5</v>
       </c>
-      <c r="S6" s="0" t="n">
-        <v>0</v>
+      <c r="S6" s="0">
+        <v>0.004995004995004995</v>
       </c>
       <c r="U6" s="0" t="s">
         <v>1552</v>
       </c>
-      <c r="V6" s="0" t="n">
-        <v>20.4166666666667</v>
-      </c>
-      <c r="W6" s="0" t="n">
-        <v>0</v>
+      <c r="V6" s="0">
+        <v>20.416666666666668</v>
+      </c>
+      <c r="W6" s="0">
+        <v>0.004995004995004995</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
         <v>1553</v>
       </c>
-      <c r="B7" s="0" t="n">
+      <c r="B7" s="0">
         <v>2.5</v>
       </c>
-      <c r="C7" s="0" t="n">
-        <v>3.005</v>
+      <c r="C7" s="0">
+        <v>3.7412587412587412</v>
       </c>
       <c r="E7" s="0" t="s">
         <v>1553</v>
       </c>
-      <c r="F7" s="0" t="n">
-        <v>4.16666666666667</v>
-      </c>
-      <c r="G7" s="0" t="n">
-        <v>0.76</v>
+      <c r="F7" s="0">
+        <v>4.1666666666666661</v>
+      </c>
+      <c r="G7" s="0">
+        <v>1.1838161838161838</v>
       </c>
       <c r="I7" s="0" t="s">
         <v>1553</v>
       </c>
-      <c r="J7" s="0" t="n">
+      <c r="J7" s="0">
         <v>3.75</v>
       </c>
-      <c r="K7" s="0" t="n">
-        <v>1.225</v>
+      <c r="K7" s="0">
+        <v>1.7432567432567434</v>
       </c>
       <c r="M7" s="0" t="s">
         <v>1553</v>
       </c>
-      <c r="N7" s="0" t="n">
-        <v>5.83333333333333</v>
-      </c>
-      <c r="O7" s="0" t="n">
-        <v>0.085</v>
+      <c r="N7" s="0">
+        <v>5.833333333333333</v>
+      </c>
+      <c r="O7" s="0">
+        <v>0.19480519480519482</v>
       </c>
       <c r="Q7" s="0" t="s">
         <v>1553</v>
       </c>
-      <c r="R7" s="0" t="n">
-        <v>11.6666666666667</v>
-      </c>
-      <c r="S7" s="0" t="n">
-        <v>0</v>
+      <c r="R7" s="0">
+        <v>11.666666666666666</v>
+      </c>
+      <c r="S7" s="0">
+        <v>0.004995004995004995</v>
       </c>
       <c r="U7" s="0" t="s">
         <v>1553</v>
       </c>
-      <c r="V7" s="0" t="n">
-        <v>5.41666666666667</v>
-      </c>
-      <c r="W7" s="0" t="n">
-        <v>0.1</v>
+      <c r="V7" s="0">
+        <v>5.416666666666667</v>
+      </c>
+      <c r="W7" s="0">
+        <v>0.19480519480519482</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
         <v>1554</v>
       </c>
-      <c r="B8" s="0" t="n">
-        <v>23.3333333333333</v>
-      </c>
-      <c r="C8" s="0" t="n">
-        <v>0</v>
+      <c r="B8" s="0">
+        <v>23.333333333333332</v>
+      </c>
+      <c r="C8" s="0">
+        <v>0.004995004995004995</v>
       </c>
       <c r="E8" s="0" t="s">
         <v>1554</v>
       </c>
-      <c r="F8" s="0" t="n">
-        <v>24.5833333333333</v>
-      </c>
-      <c r="G8" s="0" t="n">
-        <v>0</v>
+      <c r="F8" s="0">
+        <v>24.583333333333332</v>
+      </c>
+      <c r="G8" s="0">
+        <v>0.004995004995004995</v>
       </c>
       <c r="I8" s="0" t="s">
         <v>1554</v>
       </c>
-      <c r="J8" s="0" t="n">
-        <v>22.9166666666667</v>
-      </c>
-      <c r="K8" s="0" t="n">
-        <v>0</v>
+      <c r="J8" s="0">
+        <v>22.916666666666664</v>
+      </c>
+      <c r="K8" s="0">
+        <v>0.004995004995004995</v>
       </c>
       <c r="M8" s="0" t="s">
         <v>1554</v>
       </c>
-      <c r="N8" s="0" t="n">
+      <c r="N8" s="0">
         <v>18.75</v>
       </c>
-      <c r="O8" s="0" t="n">
-        <v>0</v>
+      <c r="O8" s="0">
+        <v>0.004995004995004995</v>
       </c>
       <c r="Q8" s="0" t="s">
         <v>1554</v>
       </c>
-      <c r="R8" s="0" t="n">
-        <v>25.4166666666667</v>
-      </c>
-      <c r="S8" s="0" t="n">
-        <v>0</v>
+      <c r="R8" s="0">
+        <v>25.416666666666664</v>
+      </c>
+      <c r="S8" s="0">
+        <v>0.004995004995004995</v>
       </c>
       <c r="U8" s="0" t="s">
         <v>1554</v>
       </c>
-      <c r="V8" s="0" t="n">
-        <v>9.16666666666667</v>
-      </c>
-      <c r="W8" s="0" t="n">
-        <v>0</v>
+      <c r="V8" s="0">
+        <v>9.1666666666666661</v>
+      </c>
+      <c r="W8" s="0">
+        <v>0.004995004995004995</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
         <v>1555</v>
       </c>
-      <c r="B9" s="0" t="n">
+      <c r="B9" s="0">
         <v>50</v>
       </c>
-      <c r="C9" s="0" t="n">
-        <v>0</v>
+      <c r="C9" s="0">
+        <v>0.004995004995004995</v>
       </c>
       <c r="E9" s="0" t="s">
         <v>1555</v>
       </c>
-      <c r="F9" s="0" t="n">
-        <v>43.3333333333333</v>
-      </c>
-      <c r="G9" s="0" t="n">
-        <v>0</v>
+      <c r="F9" s="0">
+        <v>43.333333333333336</v>
+      </c>
+      <c r="G9" s="0">
+        <v>0.004995004995004995</v>
       </c>
       <c r="I9" s="0" t="s">
         <v>1555</v>
       </c>
-      <c r="J9" s="0" t="n">
+      <c r="J9" s="0">
         <v>40</v>
       </c>
-      <c r="K9" s="0" t="n">
-        <v>0</v>
+      <c r="K9" s="0">
+        <v>0.004995004995004995</v>
       </c>
       <c r="M9" s="0" t="s">
         <v>1555</v>
       </c>
-      <c r="N9" s="0" t="n">
-        <v>34.5833333333333</v>
-      </c>
-      <c r="O9" s="0" t="n">
-        <v>0</v>
+      <c r="N9" s="0">
+        <v>34.583333333333336</v>
+      </c>
+      <c r="O9" s="0">
+        <v>0.004995004995004995</v>
       </c>
       <c r="Q9" s="0" t="s">
         <v>1555</v>
       </c>
-      <c r="R9" s="0" t="n">
+      <c r="R9" s="0">
         <v>30</v>
       </c>
-      <c r="S9" s="0" t="n">
-        <v>0</v>
+      <c r="S9" s="0">
+        <v>0.004995004995004995</v>
       </c>
       <c r="U9" s="0" t="s">
         <v>1555</v>
       </c>
-      <c r="V9" s="0" t="n">
+      <c r="V9" s="0">
         <v>17.5</v>
       </c>
-      <c r="W9" s="0" t="n">
-        <v>0</v>
+      <c r="W9" s="0">
+        <v>0.004995004995004995</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
         <v>1556</v>
       </c>
-      <c r="B10" s="0" t="n">
-        <v>57.0833333333333</v>
-      </c>
-      <c r="C10" s="0" t="n">
-        <v>0</v>
+      <c r="B10" s="0">
+        <v>57.083333333333329</v>
+      </c>
+      <c r="C10" s="0">
+        <v>0.004995004995004995</v>
       </c>
       <c r="E10" s="0" t="s">
         <v>1556</v>
       </c>
-      <c r="F10" s="0" t="n">
+      <c r="F10" s="0">
         <v>56.25</v>
       </c>
-      <c r="G10" s="0" t="n">
-        <v>0</v>
+      <c r="G10" s="0">
+        <v>0.004995004995004995</v>
       </c>
       <c r="I10" s="0" t="s">
         <v>1556</v>
       </c>
-      <c r="J10" s="0" t="n">
-        <v>48.3333333333333</v>
-      </c>
-      <c r="K10" s="0" t="n">
-        <v>0</v>
+      <c r="J10" s="0">
+        <v>48.333333333333336</v>
+      </c>
+      <c r="K10" s="0">
+        <v>0.004995004995004995</v>
       </c>
       <c r="M10" s="0" t="s">
         <v>1556</v>
       </c>
-      <c r="N10" s="0" t="n">
-        <v>39.5833333333333</v>
-      </c>
-      <c r="O10" s="0" t="n">
-        <v>0</v>
+      <c r="N10" s="0">
+        <v>39.583333333333329</v>
+      </c>
+      <c r="O10" s="0">
+        <v>0.004995004995004995</v>
       </c>
       <c r="Q10" s="0" t="s">
         <v>1556</v>
       </c>
-      <c r="R10" s="0" t="n">
+      <c r="R10" s="0">
         <v>30</v>
       </c>
-      <c r="S10" s="0" t="n">
-        <v>0</v>
+      <c r="S10" s="0">
+        <v>0.004995004995004995</v>
       </c>
       <c r="U10" s="0" t="s">
         <v>1556</v>
       </c>
-      <c r="V10" s="0" t="n">
-        <v>22.9166666666667</v>
-      </c>
-      <c r="W10" s="0" t="n">
-        <v>0</v>
+      <c r="V10" s="0">
+        <v>22.916666666666664</v>
+      </c>
+      <c r="W10" s="0">
+        <v>0.004995004995004995</v>
       </c>
     </row>
   </sheetData>
@@ -24844,28 +24920,34 @@
   <sheetFormatPr defaultColWidth="8.6953125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="17" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
-    <col min="2" max="2" width="20.57" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
-    <col min="3" max="3" width="22.86" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="2" max="2" width="20.5703125" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="3" max="3" width="22.85546875" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
     <col min="5" max="5" width="17" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
-    <col min="6" max="6" width="20.57" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
-    <col min="7" max="7" width="22.86" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="6" max="6" width="20.5703125" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="7" max="7" width="22.85546875" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
         <v>1502</v>
       </c>
+      <c r="B1" s="0"/>
+      <c r="C1" s="0"/>
       <c r="E1" s="0" t="s">
         <v>1503</v>
       </c>
+      <c r="F1" s="0"/>
+      <c r="G1" s="0"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="0"/>
       <c r="B2" s="0" t="s">
         <v>1512</v>
       </c>
       <c r="C2" s="0" t="s">
         <v>34</v>
       </c>
+      <c r="E2" s="0"/>
       <c r="F2" s="0" t="s">
         <v>1512</v>
       </c>
@@ -24877,240 +24959,240 @@
       <c r="A3" s="0" t="s">
         <v>1513</v>
       </c>
-      <c r="B3" s="0" t="n">
-        <v>5.84795321637427</v>
-      </c>
-      <c r="C3" s="0" t="n">
-        <v>0.028</v>
+      <c r="B3" s="0">
+        <v>5.8479532163742682</v>
+      </c>
+      <c r="C3" s="0">
+        <v>0.095904095904095904</v>
       </c>
       <c r="E3" s="0" t="s">
         <v>1513</v>
       </c>
-      <c r="F3" s="0" t="n">
-        <v>7.01754385964912</v>
-      </c>
-      <c r="G3" s="0" t="n">
-        <v>0.008</v>
+      <c r="F3" s="0">
+        <v>7.0175438596491224</v>
+      </c>
+      <c r="G3" s="0">
+        <v>0.027972027972027972</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
         <v>1514</v>
       </c>
-      <c r="B4" s="0" t="n">
-        <v>15.2046783625731</v>
-      </c>
-      <c r="C4" s="0" t="n">
-        <v>0</v>
+      <c r="B4" s="0">
+        <v>15.204678362573098</v>
+      </c>
+      <c r="C4" s="0">
+        <v>0.003996003996003996</v>
       </c>
       <c r="E4" s="0" t="s">
         <v>1514</v>
       </c>
-      <c r="F4" s="0" t="n">
-        <v>16.374269005848</v>
-      </c>
-      <c r="G4" s="0" t="n">
-        <v>0</v>
+      <c r="F4" s="0">
+        <v>16.374269005847953</v>
+      </c>
+      <c r="G4" s="0">
+        <v>0.003996003996003996</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
         <v>1515</v>
       </c>
-      <c r="B5" s="0" t="n">
-        <v>18.7134502923977</v>
-      </c>
-      <c r="C5" s="0" t="n">
-        <v>0</v>
+      <c r="B5" s="0">
+        <v>18.71345029239766</v>
+      </c>
+      <c r="C5" s="0">
+        <v>0.003996003996003996</v>
       </c>
       <c r="E5" s="0" t="s">
         <v>1515</v>
       </c>
-      <c r="F5" s="0" t="n">
-        <v>22.2222222222222</v>
-      </c>
-      <c r="G5" s="0" t="n">
-        <v>0</v>
+      <c r="F5" s="0">
+        <v>22.222222222222221</v>
+      </c>
+      <c r="G5" s="0">
+        <v>0.003996003996003996</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
         <v>1516</v>
       </c>
-      <c r="B6" s="0" t="n">
-        <v>15.2046783625731</v>
-      </c>
-      <c r="C6" s="0" t="n">
-        <v>0</v>
+      <c r="B6" s="0">
+        <v>15.204678362573098</v>
+      </c>
+      <c r="C6" s="0">
+        <v>0.003996003996003996</v>
       </c>
       <c r="E6" s="0" t="s">
         <v>1516</v>
       </c>
-      <c r="F6" s="0" t="n">
-        <v>26.9005847953216</v>
-      </c>
-      <c r="G6" s="0" t="n">
-        <v>0</v>
+      <c r="F6" s="0">
+        <v>26.900584795321635</v>
+      </c>
+      <c r="G6" s="0">
+        <v>0.003996003996003996</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
         <v>1517</v>
       </c>
-      <c r="B7" s="0" t="n">
-        <v>11.6959064327485</v>
-      </c>
-      <c r="C7" s="0" t="n">
-        <v>0</v>
+      <c r="B7" s="0">
+        <v>11.695906432748536</v>
+      </c>
+      <c r="C7" s="0">
+        <v>0.003996003996003996</v>
       </c>
       <c r="E7" s="0" t="s">
         <v>1517</v>
       </c>
-      <c r="F7" s="0" t="n">
-        <v>11.1111111111111</v>
-      </c>
-      <c r="G7" s="0" t="n">
-        <v>0</v>
+      <c r="F7" s="0">
+        <v>11.111111111111111</v>
+      </c>
+      <c r="G7" s="0">
+        <v>0.003996003996003996</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
         <v>1518</v>
       </c>
-      <c r="B8" s="0" t="n">
-        <v>19.8830409356725</v>
-      </c>
-      <c r="C8" s="0" t="n">
-        <v>0</v>
+      <c r="B8" s="0">
+        <v>19.883040935672515</v>
+      </c>
+      <c r="C8" s="0">
+        <v>0.003996003996003996</v>
       </c>
       <c r="E8" s="0" t="s">
         <v>1518</v>
       </c>
-      <c r="F8" s="0" t="n">
-        <v>22.2222222222222</v>
-      </c>
-      <c r="G8" s="0" t="n">
-        <v>0</v>
+      <c r="F8" s="0">
+        <v>22.222222222222221</v>
+      </c>
+      <c r="G8" s="0">
+        <v>0.003996003996003996</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
         <v>1519</v>
       </c>
-      <c r="B9" s="0" t="n">
-        <v>19.8830409356725</v>
-      </c>
-      <c r="C9" s="0" t="n">
-        <v>0</v>
+      <c r="B9" s="0">
+        <v>19.883040935672515</v>
+      </c>
+      <c r="C9" s="0">
+        <v>0.003996003996003996</v>
       </c>
       <c r="E9" s="0" t="s">
         <v>1519</v>
       </c>
-      <c r="F9" s="0" t="n">
-        <v>34.5029239766082</v>
-      </c>
-      <c r="G9" s="0" t="n">
-        <v>0</v>
+      <c r="F9" s="0">
+        <v>34.502923976608187</v>
+      </c>
+      <c r="G9" s="0">
+        <v>0.003996003996003996</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
         <v>1520</v>
       </c>
-      <c r="B10" s="0" t="n">
-        <v>29.8245614035088</v>
-      </c>
-      <c r="C10" s="0" t="n">
-        <v>0</v>
+      <c r="B10" s="0">
+        <v>29.82456140350877</v>
+      </c>
+      <c r="C10" s="0">
+        <v>0.003996003996003996</v>
       </c>
       <c r="E10" s="0" t="s">
         <v>1520</v>
       </c>
-      <c r="F10" s="0" t="n">
-        <v>50.2923976608187</v>
-      </c>
-      <c r="G10" s="0" t="n">
-        <v>0</v>
+      <c r="F10" s="0">
+        <v>50.292397660818708</v>
+      </c>
+      <c r="G10" s="0">
+        <v>0.003996003996003996</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
         <v>1521</v>
       </c>
-      <c r="B11" s="0" t="n">
-        <v>11.6959064327485</v>
-      </c>
-      <c r="C11" s="0" t="n">
-        <v>0</v>
+      <c r="B11" s="0">
+        <v>11.695906432748536</v>
+      </c>
+      <c r="C11" s="0">
+        <v>0.003996003996003996</v>
       </c>
       <c r="E11" s="0" t="s">
         <v>1521</v>
       </c>
-      <c r="F11" s="0" t="n">
-        <v>11.1111111111111</v>
-      </c>
-      <c r="G11" s="0" t="n">
-        <v>0</v>
+      <c r="F11" s="0">
+        <v>11.111111111111111</v>
+      </c>
+      <c r="G11" s="0">
+        <v>0.003996003996003996</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="0" t="s">
         <v>1522</v>
       </c>
-      <c r="B12" s="0" t="n">
-        <v>15.7894736842105</v>
-      </c>
-      <c r="C12" s="0" t="n">
-        <v>0</v>
+      <c r="B12" s="0">
+        <v>15.789473684210526</v>
+      </c>
+      <c r="C12" s="0">
+        <v>0.003996003996003996</v>
       </c>
       <c r="E12" s="0" t="s">
         <v>1522</v>
       </c>
-      <c r="F12" s="0" t="n">
-        <v>16.374269005848</v>
-      </c>
-      <c r="G12" s="0" t="n">
-        <v>0</v>
+      <c r="F12" s="0">
+        <v>16.374269005847953</v>
+      </c>
+      <c r="G12" s="0">
+        <v>0.003996003996003996</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="0" t="s">
         <v>1523</v>
       </c>
-      <c r="B13" s="0" t="n">
-        <v>27.4853801169591</v>
-      </c>
-      <c r="C13" s="0" t="n">
-        <v>0</v>
+      <c r="B13" s="0">
+        <v>27.485380116959064</v>
+      </c>
+      <c r="C13" s="0">
+        <v>0.003996003996003996</v>
       </c>
       <c r="E13" s="0" t="s">
         <v>1523</v>
       </c>
-      <c r="F13" s="0" t="n">
-        <v>38.0116959064327</v>
-      </c>
-      <c r="G13" s="0" t="n">
-        <v>0</v>
+      <c r="F13" s="0">
+        <v>38.011695906432749</v>
+      </c>
+      <c r="G13" s="0">
+        <v>0.003996003996003996</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="0" t="s">
         <v>1524</v>
       </c>
-      <c r="B14" s="0" t="n">
-        <v>36.2573099415205</v>
-      </c>
-      <c r="C14" s="0" t="n">
-        <v>0</v>
+      <c r="B14" s="0">
+        <v>36.257309941520468</v>
+      </c>
+      <c r="C14" s="0">
+        <v>0.003996003996003996</v>
       </c>
       <c r="E14" s="0" t="s">
         <v>1524</v>
       </c>
-      <c r="F14" s="0" t="n">
-        <v>50.2923976608187</v>
-      </c>
-      <c r="G14" s="0" t="n">
-        <v>0</v>
+      <c r="F14" s="0">
+        <v>50.292397660818708</v>
+      </c>
+      <c r="G14" s="0">
+        <v>0.003996003996003996</v>
       </c>
     </row>
   </sheetData>
@@ -25132,29 +25214,35 @@
   <dimension ref="A1:G14"/>
   <sheetFormatPr defaultColWidth="8.6953125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="10.99" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
-    <col min="2" max="2" width="20.57" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
-    <col min="3" max="3" width="22.86" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
-    <col min="5" max="5" width="10.99" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
-    <col min="6" max="6" width="20.57" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
-    <col min="7" max="7" width="22.86" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="1" max="1" width="11" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="2" max="2" width="20.5703125" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="3" max="3" width="22.85546875" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="5" max="5" width="11" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="6" max="6" width="20.5703125" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="7" max="7" width="22.85546875" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
         <v>1502</v>
       </c>
+      <c r="B1" s="0"/>
+      <c r="C1" s="0"/>
       <c r="E1" s="0" t="s">
         <v>1503</v>
       </c>
+      <c r="F1" s="0"/>
+      <c r="G1" s="0"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="0"/>
       <c r="B2" s="0" t="s">
         <v>1512</v>
       </c>
       <c r="C2" s="0" t="s">
         <v>34</v>
       </c>
+      <c r="E2" s="0"/>
       <c r="F2" s="0" t="s">
         <v>1512</v>
       </c>
@@ -25166,240 +25254,240 @@
       <c r="A3" s="0" t="s">
         <v>1525</v>
       </c>
-      <c r="B3" s="0" t="n">
-        <v>11.6959064327485</v>
-      </c>
-      <c r="C3" s="0" t="n">
-        <v>0</v>
+      <c r="B3" s="0">
+        <v>11.695906432748536</v>
+      </c>
+      <c r="C3" s="0">
+        <v>0.003996003996003996</v>
       </c>
       <c r="E3" s="0" t="s">
         <v>1525</v>
       </c>
-      <c r="F3" s="0" t="n">
-        <v>9.35672514619883</v>
-      </c>
-      <c r="G3" s="0" t="n">
-        <v>0</v>
+      <c r="F3" s="0">
+        <v>9.3567251461988299</v>
+      </c>
+      <c r="G3" s="0">
+        <v>0.003996003996003996</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
         <v>1526</v>
       </c>
-      <c r="B4" s="0" t="n">
-        <v>16.374269005848</v>
-      </c>
-      <c r="C4" s="0" t="n">
-        <v>0</v>
+      <c r="B4" s="0">
+        <v>16.374269005847953</v>
+      </c>
+      <c r="C4" s="0">
+        <v>0.003996003996003996</v>
       </c>
       <c r="E4" s="0" t="s">
         <v>1526</v>
       </c>
-      <c r="F4" s="0" t="n">
-        <v>19.2982456140351</v>
-      </c>
-      <c r="G4" s="0" t="n">
-        <v>0</v>
+      <c r="F4" s="0">
+        <v>19.298245614035086</v>
+      </c>
+      <c r="G4" s="0">
+        <v>0.003996003996003996</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
         <v>1527</v>
       </c>
-      <c r="B5" s="0" t="n">
-        <v>15.2046783625731</v>
-      </c>
-      <c r="C5" s="0" t="n">
-        <v>0</v>
+      <c r="B5" s="0">
+        <v>15.204678362573098</v>
+      </c>
+      <c r="C5" s="0">
+        <v>0.003996003996003996</v>
       </c>
       <c r="E5" s="0" t="s">
         <v>1527</v>
       </c>
-      <c r="F5" s="0" t="n">
-        <v>11.6959064327485</v>
-      </c>
-      <c r="G5" s="0" t="n">
-        <v>0</v>
+      <c r="F5" s="0">
+        <v>11.695906432748536</v>
+      </c>
+      <c r="G5" s="0">
+        <v>0.003996003996003996</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
         <v>1528</v>
       </c>
-      <c r="B6" s="0" t="n">
-        <v>15.7894736842105</v>
-      </c>
-      <c r="C6" s="0" t="n">
-        <v>0</v>
+      <c r="B6" s="0">
+        <v>15.789473684210526</v>
+      </c>
+      <c r="C6" s="0">
+        <v>0.003996003996003996</v>
       </c>
       <c r="E6" s="0" t="s">
         <v>1528</v>
       </c>
-      <c r="F6" s="0" t="n">
-        <v>19.2982456140351</v>
-      </c>
-      <c r="G6" s="0" t="n">
-        <v>0</v>
+      <c r="F6" s="0">
+        <v>19.298245614035086</v>
+      </c>
+      <c r="G6" s="0">
+        <v>0.003996003996003996</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
         <v>1529</v>
       </c>
-      <c r="B7" s="0" t="n">
-        <v>8.18713450292398</v>
-      </c>
-      <c r="C7" s="0" t="n">
-        <v>0</v>
+      <c r="B7" s="0">
+        <v>8.1871345029239766</v>
+      </c>
+      <c r="C7" s="0">
+        <v>0.003996003996003996</v>
       </c>
       <c r="E7" s="0" t="s">
         <v>1529</v>
       </c>
-      <c r="F7" s="0" t="n">
-        <v>7.60233918128655</v>
-      </c>
-      <c r="G7" s="0" t="n">
-        <v>0.004</v>
+      <c r="F7" s="0">
+        <v>7.6023391812865491</v>
+      </c>
+      <c r="G7" s="0">
+        <v>0.011988011988011988</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
         <v>1530</v>
       </c>
-      <c r="B8" s="0" t="n">
-        <v>19.2982456140351</v>
-      </c>
-      <c r="C8" s="0" t="n">
-        <v>0</v>
+      <c r="B8" s="0">
+        <v>19.298245614035086</v>
+      </c>
+      <c r="C8" s="0">
+        <v>0.003996003996003996</v>
       </c>
       <c r="E8" s="0" t="s">
         <v>1530</v>
       </c>
-      <c r="F8" s="0" t="n">
-        <v>22.2222222222222</v>
-      </c>
-      <c r="G8" s="0" t="n">
-        <v>0</v>
+      <c r="F8" s="0">
+        <v>22.222222222222221</v>
+      </c>
+      <c r="G8" s="0">
+        <v>0.003996003996003996</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
         <v>1531</v>
       </c>
-      <c r="B9" s="0" t="n">
-        <v>19.8830409356725</v>
-      </c>
-      <c r="C9" s="0" t="n">
-        <v>0</v>
+      <c r="B9" s="0">
+        <v>19.883040935672515</v>
+      </c>
+      <c r="C9" s="0">
+        <v>0.003996003996003996</v>
       </c>
       <c r="E9" s="0" t="s">
         <v>1531</v>
       </c>
-      <c r="F9" s="0" t="n">
-        <v>23.3918128654971</v>
-      </c>
-      <c r="G9" s="0" t="n">
-        <v>0</v>
+      <c r="F9" s="0">
+        <v>23.391812865497073</v>
+      </c>
+      <c r="G9" s="0">
+        <v>0.003996003996003996</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
         <v>1532</v>
       </c>
-      <c r="B10" s="0" t="n">
-        <v>22.2222222222222</v>
-      </c>
-      <c r="C10" s="0" t="n">
-        <v>0</v>
+      <c r="B10" s="0">
+        <v>22.222222222222221</v>
+      </c>
+      <c r="C10" s="0">
+        <v>0.003996003996003996</v>
       </c>
       <c r="E10" s="0" t="s">
         <v>1532</v>
       </c>
-      <c r="F10" s="0" t="n">
-        <v>23.3918128654971</v>
-      </c>
-      <c r="G10" s="0" t="n">
-        <v>0</v>
+      <c r="F10" s="0">
+        <v>23.391812865497073</v>
+      </c>
+      <c r="G10" s="0">
+        <v>0.003996003996003996</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
         <v>1533</v>
       </c>
-      <c r="B11" s="0" t="n">
-        <v>7.60233918128655</v>
-      </c>
-      <c r="C11" s="0" t="n">
-        <v>0</v>
+      <c r="B11" s="0">
+        <v>7.6023391812865491</v>
+      </c>
+      <c r="C11" s="0">
+        <v>0.003996003996003996</v>
       </c>
       <c r="E11" s="0" t="s">
         <v>1533</v>
       </c>
-      <c r="F11" s="0" t="n">
-        <v>6.4327485380117</v>
-      </c>
-      <c r="G11" s="0" t="n">
-        <v>0.028</v>
+      <c r="F11" s="0">
+        <v>6.4327485380116958</v>
+      </c>
+      <c r="G11" s="0">
+        <v>0.059940059940059943</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="0" t="s">
         <v>1534</v>
       </c>
-      <c r="B12" s="0" t="n">
-        <v>16.9590643274854</v>
-      </c>
-      <c r="C12" s="0" t="n">
-        <v>0</v>
+      <c r="B12" s="0">
+        <v>16.959064327485379</v>
+      </c>
+      <c r="C12" s="0">
+        <v>0.003996003996003996</v>
       </c>
       <c r="E12" s="0" t="s">
         <v>1534</v>
       </c>
-      <c r="F12" s="0" t="n">
-        <v>21.6374269005848</v>
-      </c>
-      <c r="G12" s="0" t="n">
-        <v>0</v>
+      <c r="F12" s="0">
+        <v>21.637426900584796</v>
+      </c>
+      <c r="G12" s="0">
+        <v>0.003996003996003996</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="0" t="s">
         <v>1535</v>
       </c>
-      <c r="B13" s="0" t="n">
-        <v>24.5614035087719</v>
-      </c>
-      <c r="C13" s="0" t="n">
-        <v>0</v>
+      <c r="B13" s="0">
+        <v>24.561403508771928</v>
+      </c>
+      <c r="C13" s="0">
+        <v>0.003996003996003996</v>
       </c>
       <c r="E13" s="0" t="s">
         <v>1535</v>
       </c>
-      <c r="F13" s="0" t="n">
-        <v>37.4269005847953</v>
-      </c>
-      <c r="G13" s="0" t="n">
-        <v>0</v>
+      <c r="F13" s="0">
+        <v>37.42690058479532</v>
+      </c>
+      <c r="G13" s="0">
+        <v>0.003996003996003996</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="0" t="s">
         <v>1536</v>
       </c>
-      <c r="B14" s="0" t="n">
-        <v>23.3918128654971</v>
-      </c>
-      <c r="C14" s="0" t="n">
-        <v>0</v>
+      <c r="B14" s="0">
+        <v>23.391812865497073</v>
+      </c>
+      <c r="C14" s="0">
+        <v>0.003996003996003996</v>
       </c>
       <c r="E14" s="0" t="s">
         <v>1536</v>
       </c>
-      <c r="F14" s="0" t="n">
-        <v>31.5789473684211</v>
-      </c>
-      <c r="G14" s="0" t="n">
-        <v>0</v>
+      <c r="F14" s="0">
+        <v>31.578947368421051</v>
+      </c>
+      <c r="G14" s="0">
+        <v>0.003996003996003996</v>
       </c>
     </row>
   </sheetData>
@@ -25421,29 +25509,35 @@
   <dimension ref="A1:G14"/>
   <sheetFormatPr defaultColWidth="8.6953125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="14.57" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
-    <col min="2" max="2" width="20.57" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
-    <col min="3" max="3" width="22.86" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
-    <col min="5" max="5" width="14.57" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
-    <col min="6" max="6" width="20.57" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
-    <col min="7" max="7" width="22.86" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="1" max="1" width="14.5703125" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="2" max="2" width="20.5703125" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="3" max="3" width="22.85546875" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="5" max="5" width="14.5703125" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="6" max="6" width="20.5703125" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="7" max="7" width="22.85546875" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
         <v>1502</v>
       </c>
+      <c r="B1" s="0"/>
+      <c r="C1" s="0"/>
       <c r="E1" s="0" t="s">
         <v>1503</v>
       </c>
+      <c r="F1" s="0"/>
+      <c r="G1" s="0"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="0"/>
       <c r="B2" s="0" t="s">
         <v>1512</v>
       </c>
       <c r="C2" s="0" t="s">
         <v>34</v>
       </c>
+      <c r="E2" s="0"/>
       <c r="F2" s="0" t="s">
         <v>1512</v>
       </c>
@@ -25455,240 +25549,240 @@
       <c r="A3" s="0" t="s">
         <v>1537</v>
       </c>
-      <c r="B3" s="0" t="n">
-        <v>4.09356725146199</v>
-      </c>
-      <c r="C3" s="0" t="n">
-        <v>0.636</v>
+      <c r="B3" s="0">
+        <v>4.0935672514619883</v>
+      </c>
+      <c r="C3" s="0">
+        <v>0.89110889110889113</v>
       </c>
       <c r="E3" s="0" t="s">
         <v>1537</v>
       </c>
-      <c r="F3" s="0" t="n">
-        <v>4.09356725146199</v>
-      </c>
-      <c r="G3" s="0" t="n">
-        <v>0.544</v>
+      <c r="F3" s="0">
+        <v>4.0935672514619883</v>
+      </c>
+      <c r="G3" s="0">
+        <v>0.83916083916083917</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
         <v>1538</v>
       </c>
-      <c r="B4" s="0" t="n">
-        <v>15.2046783625731</v>
-      </c>
-      <c r="C4" s="0" t="n">
-        <v>0</v>
+      <c r="B4" s="0">
+        <v>15.204678362573098</v>
+      </c>
+      <c r="C4" s="0">
+        <v>0.003996003996003996</v>
       </c>
       <c r="E4" s="0" t="s">
         <v>1538</v>
       </c>
-      <c r="F4" s="0" t="n">
-        <v>14.6198830409357</v>
-      </c>
-      <c r="G4" s="0" t="n">
-        <v>0</v>
+      <c r="F4" s="0">
+        <v>14.619883040935672</v>
+      </c>
+      <c r="G4" s="0">
+        <v>0.003996003996003996</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
         <v>1539</v>
       </c>
-      <c r="B5" s="0" t="n">
-        <v>16.9590643274854</v>
-      </c>
-      <c r="C5" s="0" t="n">
-        <v>0</v>
+      <c r="B5" s="0">
+        <v>16.959064327485379</v>
+      </c>
+      <c r="C5" s="0">
+        <v>0.003996003996003996</v>
       </c>
       <c r="E5" s="0" t="s">
         <v>1539</v>
       </c>
-      <c r="F5" s="0" t="n">
-        <v>20.4678362573099</v>
-      </c>
-      <c r="G5" s="0" t="n">
-        <v>0</v>
+      <c r="F5" s="0">
+        <v>20.467836257309941</v>
+      </c>
+      <c r="G5" s="0">
+        <v>0.003996003996003996</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
         <v>1540</v>
       </c>
-      <c r="B6" s="0" t="n">
-        <v>13.4502923976608</v>
-      </c>
-      <c r="C6" s="0" t="n">
-        <v>0</v>
+      <c r="B6" s="0">
+        <v>13.450292397660817</v>
+      </c>
+      <c r="C6" s="0">
+        <v>0.003996003996003996</v>
       </c>
       <c r="E6" s="0" t="s">
         <v>1540</v>
       </c>
-      <c r="F6" s="0" t="n">
-        <v>22.2222222222222</v>
-      </c>
-      <c r="G6" s="0" t="n">
-        <v>0</v>
+      <c r="F6" s="0">
+        <v>22.222222222222221</v>
+      </c>
+      <c r="G6" s="0">
+        <v>0.003996003996003996</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
         <v>1541</v>
       </c>
-      <c r="B7" s="0" t="n">
-        <v>5.26315789473684</v>
-      </c>
-      <c r="C7" s="0" t="n">
-        <v>0.16</v>
+      <c r="B7" s="0">
+        <v>5.2631578947368416</v>
+      </c>
+      <c r="C7" s="0">
+        <v>0.33566433566433568</v>
       </c>
       <c r="E7" s="0" t="s">
         <v>1541</v>
       </c>
-      <c r="F7" s="0" t="n">
-        <v>4.09356725146199</v>
-      </c>
-      <c r="G7" s="0" t="n">
-        <v>0.432</v>
+      <c r="F7" s="0">
+        <v>4.0935672514619883</v>
+      </c>
+      <c r="G7" s="0">
+        <v>0.75924075924075929</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
         <v>1542</v>
       </c>
-      <c r="B8" s="0" t="n">
-        <v>15.7894736842105</v>
-      </c>
-      <c r="C8" s="0" t="n">
-        <v>0</v>
+      <c r="B8" s="0">
+        <v>15.789473684210526</v>
+      </c>
+      <c r="C8" s="0">
+        <v>0.003996003996003996</v>
       </c>
       <c r="E8" s="0" t="s">
         <v>1542</v>
       </c>
-      <c r="F8" s="0" t="n">
-        <v>15.2046783625731</v>
-      </c>
-      <c r="G8" s="0" t="n">
-        <v>0</v>
+      <c r="F8" s="0">
+        <v>15.204678362573098</v>
+      </c>
+      <c r="G8" s="0">
+        <v>0.003996003996003996</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
         <v>1543</v>
       </c>
-      <c r="B9" s="0" t="n">
-        <v>28.0701754385965</v>
-      </c>
-      <c r="C9" s="0" t="n">
-        <v>0</v>
+      <c r="B9" s="0">
+        <v>28.07017543859649</v>
+      </c>
+      <c r="C9" s="0">
+        <v>0.003996003996003996</v>
       </c>
       <c r="E9" s="0" t="s">
         <v>1543</v>
       </c>
-      <c r="F9" s="0" t="n">
-        <v>29.8245614035088</v>
-      </c>
-      <c r="G9" s="0" t="n">
-        <v>0</v>
+      <c r="F9" s="0">
+        <v>29.82456140350877</v>
+      </c>
+      <c r="G9" s="0">
+        <v>0.003996003996003996</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
         <v>1544</v>
       </c>
-      <c r="B10" s="0" t="n">
-        <v>27.4853801169591</v>
-      </c>
-      <c r="C10" s="0" t="n">
-        <v>0</v>
+      <c r="B10" s="0">
+        <v>27.485380116959064</v>
+      </c>
+      <c r="C10" s="0">
+        <v>0.003996003996003996</v>
       </c>
       <c r="E10" s="0" t="s">
         <v>1544</v>
       </c>
-      <c r="F10" s="0" t="n">
-        <v>33.3333333333333</v>
-      </c>
-      <c r="G10" s="0" t="n">
-        <v>0</v>
+      <c r="F10" s="0">
+        <v>33.333333333333329</v>
+      </c>
+      <c r="G10" s="0">
+        <v>0.003996003996003996</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
         <v>1545</v>
       </c>
-      <c r="B11" s="0" t="n">
-        <v>5.26315789473684</v>
-      </c>
-      <c r="C11" s="0" t="n">
-        <v>0.256</v>
+      <c r="B11" s="0">
+        <v>5.2631578947368416</v>
+      </c>
+      <c r="C11" s="0">
+        <v>0.39560439560439559</v>
       </c>
       <c r="E11" s="0" t="s">
         <v>1545</v>
       </c>
-      <c r="F11" s="0" t="n">
-        <v>4.09356725146199</v>
-      </c>
-      <c r="G11" s="0" t="n">
-        <v>0.5</v>
+      <c r="F11" s="0">
+        <v>4.0935672514619883</v>
+      </c>
+      <c r="G11" s="0">
+        <v>0.79520479520479526</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="0" t="s">
         <v>1546</v>
       </c>
-      <c r="B12" s="0" t="n">
-        <v>15.2046783625731</v>
-      </c>
-      <c r="C12" s="0" t="n">
-        <v>0</v>
+      <c r="B12" s="0">
+        <v>15.204678362573098</v>
+      </c>
+      <c r="C12" s="0">
+        <v>0.003996003996003996</v>
       </c>
       <c r="E12" s="0" t="s">
         <v>1546</v>
       </c>
-      <c r="F12" s="0" t="n">
-        <v>14.0350877192982</v>
-      </c>
-      <c r="G12" s="0" t="n">
-        <v>0</v>
+      <c r="F12" s="0">
+        <v>14.035087719298245</v>
+      </c>
+      <c r="G12" s="0">
+        <v>0.003996003996003996</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="0" t="s">
         <v>1547</v>
       </c>
-      <c r="B13" s="0" t="n">
-        <v>24.5614035087719</v>
-      </c>
-      <c r="C13" s="0" t="n">
-        <v>0</v>
+      <c r="B13" s="0">
+        <v>24.561403508771928</v>
+      </c>
+      <c r="C13" s="0">
+        <v>0.003996003996003996</v>
       </c>
       <c r="E13" s="0" t="s">
         <v>1547</v>
       </c>
-      <c r="F13" s="0" t="n">
-        <v>26.9005847953216</v>
-      </c>
-      <c r="G13" s="0" t="n">
-        <v>0</v>
+      <c r="F13" s="0">
+        <v>26.900584795321635</v>
+      </c>
+      <c r="G13" s="0">
+        <v>0.003996003996003996</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="0" t="s">
         <v>1548</v>
       </c>
-      <c r="B14" s="0" t="n">
-        <v>21.6374269005848</v>
-      </c>
-      <c r="C14" s="0" t="n">
-        <v>0</v>
+      <c r="B14" s="0">
+        <v>21.637426900584796</v>
+      </c>
+      <c r="C14" s="0">
+        <v>0.003996003996003996</v>
       </c>
       <c r="E14" s="0" t="s">
         <v>1548</v>
       </c>
-      <c r="F14" s="0" t="n">
-        <v>26.9005847953216</v>
-      </c>
-      <c r="G14" s="0" t="n">
-        <v>0</v>
+      <c r="F14" s="0">
+        <v>26.900584795321635</v>
+      </c>
+      <c r="G14" s="0">
+        <v>0.003996003996003996</v>
       </c>
     </row>
   </sheetData>
@@ -25710,29 +25804,35 @@
   <dimension ref="A1:G10"/>
   <sheetFormatPr defaultColWidth="8.6953125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="14.86" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
-    <col min="2" max="2" width="20.57" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
-    <col min="3" max="3" width="22.86" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
-    <col min="5" max="5" width="14.86" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
-    <col min="6" max="6" width="20.57" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
-    <col min="7" max="7" width="22.86" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="1" max="1" width="14.85546875" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="2" max="2" width="20.5703125" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="3" max="3" width="22.85546875" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="5" max="5" width="14.85546875" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="6" max="6" width="20.5703125" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="7" max="7" width="22.85546875" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
         <v>1502</v>
       </c>
+      <c r="B1" s="0"/>
+      <c r="C1" s="0"/>
       <c r="E1" s="0" t="s">
         <v>1503</v>
       </c>
+      <c r="F1" s="0"/>
+      <c r="G1" s="0"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="0"/>
       <c r="B2" s="0" t="s">
         <v>1512</v>
       </c>
       <c r="C2" s="0" t="s">
         <v>34</v>
       </c>
+      <c r="E2" s="0"/>
       <c r="F2" s="0" t="s">
         <v>1512</v>
       </c>
@@ -25744,160 +25844,160 @@
       <c r="A3" s="0" t="s">
         <v>1549</v>
       </c>
-      <c r="B3" s="0" t="n">
-        <v>5.26315789473684</v>
-      </c>
-      <c r="C3" s="0" t="n">
-        <v>0.236</v>
+      <c r="B3" s="0">
+        <v>5.2631578947368416</v>
+      </c>
+      <c r="C3" s="0">
+        <v>0.37562437562437562</v>
       </c>
       <c r="E3" s="0" t="s">
         <v>1549</v>
       </c>
-      <c r="F3" s="0" t="n">
-        <v>3.50877192982456</v>
-      </c>
-      <c r="G3" s="0" t="n">
-        <v>0.992</v>
+      <c r="F3" s="0">
+        <v>3.5087719298245612</v>
+      </c>
+      <c r="G3" s="0">
+        <v>1.3706293706293706</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
         <v>1550</v>
       </c>
-      <c r="B4" s="0" t="n">
-        <v>15.7894736842105</v>
-      </c>
-      <c r="C4" s="0" t="n">
-        <v>0</v>
+      <c r="B4" s="0">
+        <v>15.789473684210526</v>
+      </c>
+      <c r="C4" s="0">
+        <v>0.003996003996003996</v>
       </c>
       <c r="E4" s="0" t="s">
         <v>1550</v>
       </c>
-      <c r="F4" s="0" t="n">
-        <v>18.1286549707602</v>
-      </c>
-      <c r="G4" s="0" t="n">
-        <v>0</v>
+      <c r="F4" s="0">
+        <v>18.128654970760234</v>
+      </c>
+      <c r="G4" s="0">
+        <v>0.003996003996003996</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
         <v>1551</v>
       </c>
-      <c r="B5" s="0" t="n">
-        <v>22.8070175438596</v>
-      </c>
-      <c r="C5" s="0" t="n">
-        <v>0</v>
+      <c r="B5" s="0">
+        <v>22.807017543859647</v>
+      </c>
+      <c r="C5" s="0">
+        <v>0.003996003996003996</v>
       </c>
       <c r="E5" s="0" t="s">
         <v>1551</v>
       </c>
-      <c r="F5" s="0" t="n">
-        <v>24.5614035087719</v>
-      </c>
-      <c r="G5" s="0" t="n">
-        <v>0</v>
+      <c r="F5" s="0">
+        <v>24.561403508771928</v>
+      </c>
+      <c r="G5" s="0">
+        <v>0.003996003996003996</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
         <v>1552</v>
       </c>
-      <c r="B6" s="0" t="n">
-        <v>25.1461988304094</v>
-      </c>
-      <c r="C6" s="0" t="n">
-        <v>0</v>
+      <c r="B6" s="0">
+        <v>25.146198830409354</v>
+      </c>
+      <c r="C6" s="0">
+        <v>0.003996003996003996</v>
       </c>
       <c r="E6" s="0" t="s">
         <v>1552</v>
       </c>
-      <c r="F6" s="0" t="n">
-        <v>27.4853801169591</v>
-      </c>
-      <c r="G6" s="0" t="n">
-        <v>0</v>
+      <c r="F6" s="0">
+        <v>27.485380116959064</v>
+      </c>
+      <c r="G6" s="0">
+        <v>0.003996003996003996</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
         <v>1553</v>
       </c>
-      <c r="B7" s="0" t="n">
-        <v>7.01754385964912</v>
-      </c>
-      <c r="C7" s="0" t="n">
-        <v>0.028</v>
+      <c r="B7" s="0">
+        <v>7.0175438596491224</v>
+      </c>
+      <c r="C7" s="0">
+        <v>0.063936063936063936</v>
       </c>
       <c r="E7" s="0" t="s">
         <v>1553</v>
       </c>
-      <c r="F7" s="0" t="n">
-        <v>3.50877192982456</v>
-      </c>
-      <c r="G7" s="0" t="n">
-        <v>0.928</v>
+      <c r="F7" s="0">
+        <v>3.5087719298245612</v>
+      </c>
+      <c r="G7" s="0">
+        <v>1.3466533466533466</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
         <v>1554</v>
       </c>
-      <c r="B8" s="0" t="n">
-        <v>15.7894736842105</v>
-      </c>
-      <c r="C8" s="0" t="n">
-        <v>0</v>
+      <c r="B8" s="0">
+        <v>15.789473684210526</v>
+      </c>
+      <c r="C8" s="0">
+        <v>0.003996003996003996</v>
       </c>
       <c r="E8" s="0" t="s">
         <v>1554</v>
       </c>
-      <c r="F8" s="0" t="n">
-        <v>19.8830409356725</v>
-      </c>
-      <c r="G8" s="0" t="n">
-        <v>0</v>
+      <c r="F8" s="0">
+        <v>19.883040935672515</v>
+      </c>
+      <c r="G8" s="0">
+        <v>0.003996003996003996</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
         <v>1555</v>
       </c>
-      <c r="B9" s="0" t="n">
-        <v>22.2222222222222</v>
-      </c>
-      <c r="C9" s="0" t="n">
-        <v>0</v>
+      <c r="B9" s="0">
+        <v>22.222222222222221</v>
+      </c>
+      <c r="C9" s="0">
+        <v>0.003996003996003996</v>
       </c>
       <c r="E9" s="0" t="s">
         <v>1555</v>
       </c>
-      <c r="F9" s="0" t="n">
-        <v>28.0701754385965</v>
-      </c>
-      <c r="G9" s="0" t="n">
-        <v>0</v>
+      <c r="F9" s="0">
+        <v>28.07017543859649</v>
+      </c>
+      <c r="G9" s="0">
+        <v>0.003996003996003996</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
         <v>1556</v>
       </c>
-      <c r="B10" s="0" t="n">
-        <v>25.1461988304094</v>
-      </c>
-      <c r="C10" s="0" t="n">
-        <v>0</v>
+      <c r="B10" s="0">
+        <v>25.146198830409354</v>
+      </c>
+      <c r="C10" s="0">
+        <v>0.003996003996003996</v>
       </c>
       <c r="E10" s="0" t="s">
         <v>1556</v>
       </c>
-      <c r="F10" s="0" t="n">
-        <v>30.9941520467836</v>
-      </c>
-      <c r="G10" s="0" t="n">
-        <v>0</v>
+      <c r="F10" s="0">
+        <v>30.994152046783626</v>
+      </c>
+      <c r="G10" s="0">
+        <v>0.003996003996003996</v>
       </c>
     </row>
   </sheetData>
@@ -30601,9 +30701,9 @@
     <col min="2" max="2" width="11.99" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
     <col min="3" max="3" width="3.14" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
     <col min="4" max="4" width="22.86" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
-    <col min="6" max="6" width="11.71" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
-    <col min="7" max="7" width="16.29" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
-    <col min="8" max="8" width="22.86" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="6" max="6" width="11.7109375" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="7" max="7" width="16.28515625" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="8" max="8" width="22.85546875" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30616,6 +30716,7 @@
       <c r="D1" s="0" t="s">
         <v>34</v>
       </c>
+      <c r="F1" s="0"/>
       <c r="G1" s="0" t="s">
         <v>57</v>
       </c>
@@ -30642,8 +30743,8 @@
       <c r="G2" s="0" t="s">
         <v>59</v>
       </c>
-      <c r="H2" s="0" t="n">
-        <v>0</v>
+      <c r="H2" s="0">
+        <v>0.0054972513743128436</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30665,8 +30766,8 @@
       <c r="G3" s="0" t="s">
         <v>61</v>
       </c>
-      <c r="H3" s="0" t="n">
-        <v>0</v>
+      <c r="H3" s="0">
+        <v>0.0054972513743128436</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30688,8 +30789,8 @@
       <c r="G4" s="0" t="s">
         <v>63</v>
       </c>
-      <c r="H4" s="0" t="n">
-        <v>0</v>
+      <c r="H4" s="0">
+        <v>0.0054972513743128436</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30711,8 +30812,8 @@
       <c r="G5" s="0" t="s">
         <v>65</v>
       </c>
-      <c r="H5" s="0" t="n">
-        <v>0</v>
+      <c r="H5" s="0">
+        <v>0.0054972513743128436</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30734,8 +30835,8 @@
       <c r="G6" s="0" t="s">
         <v>67</v>
       </c>
-      <c r="H6" s="0" t="n">
-        <v>0.0165</v>
+      <c r="H6" s="0">
+        <v>0.021989005497251375</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30757,8 +30858,8 @@
       <c r="G7" s="0" t="s">
         <v>69</v>
       </c>
-      <c r="H7" s="0" t="n">
-        <v>0</v>
+      <c r="H7" s="0">
+        <v>0.0054972513743128436</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30780,8 +30881,8 @@
       <c r="G8" s="0" t="s">
         <v>71</v>
       </c>
-      <c r="H8" s="0" t="n">
-        <v>0.1815</v>
+      <c r="H8" s="0">
+        <v>0.18690654672663667</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30803,8 +30904,8 @@
       <c r="G9" s="0" t="s">
         <v>73</v>
       </c>
-      <c r="H9" s="0" t="n">
-        <v>0.0055</v>
+      <c r="H9" s="0">
+        <v>0.010994502748625687</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30826,8 +30927,8 @@
       <c r="G10" s="0" t="s">
         <v>75</v>
       </c>
-      <c r="H10" s="0" t="n">
-        <v>1.3915</v>
+      <c r="H10" s="0">
+        <v>1.3963018490754624</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30849,8 +30950,8 @@
       <c r="G11" s="0" t="s">
         <v>77</v>
       </c>
-      <c r="H11" s="0" t="n">
-        <v>0</v>
+      <c r="H11" s="0">
+        <v>0.0054972513743128436</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30872,8 +30973,8 @@
       <c r="G12" s="0" t="s">
         <v>79</v>
       </c>
-      <c r="H12" s="0" t="n">
-        <v>0</v>
+      <c r="H12" s="0">
+        <v>0.0054972513743128436</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30889,6 +30990,7 @@
       <c r="G13" s="0" t="s">
         <v>81</v>
       </c>
+      <c r="H13" s="0"/>
     </row>
   </sheetData>
   <printOptions horizontalCentered="false" verticalCentered="false" headings="false" gridLines="false" gridLinesSet="true"/>
@@ -38533,9 +38635,9 @@
     <col min="2" max="2" width="11.99" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
     <col min="3" max="3" width="3.14" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
     <col min="4" max="4" width="22.86" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
-    <col min="6" max="6" width="11.71" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
-    <col min="7" max="7" width="16.29" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
-    <col min="8" max="8" width="22.86" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="6" max="6" width="11.7109375" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="7" max="7" width="16.28515625" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="8" max="8" width="22.85546875" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -38548,6 +38650,7 @@
       <c r="D1" s="0" t="s">
         <v>34</v>
       </c>
+      <c r="F1" s="0"/>
       <c r="G1" s="0" t="s">
         <v>57</v>
       </c>
@@ -38574,8 +38677,8 @@
       <c r="G2" s="0" t="s">
         <v>83</v>
       </c>
-      <c r="H2" s="0" t="n">
-        <v>0</v>
+      <c r="H2" s="0">
+        <v>0.0054972513743128436</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -38597,8 +38700,8 @@
       <c r="G3" s="0" t="s">
         <v>85</v>
       </c>
-      <c r="H3" s="0" t="n">
-        <v>0</v>
+      <c r="H3" s="0">
+        <v>0.0054972513743128436</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -38620,8 +38723,8 @@
       <c r="G4" s="0" t="s">
         <v>87</v>
       </c>
-      <c r="H4" s="0" t="n">
-        <v>0</v>
+      <c r="H4" s="0">
+        <v>0.0054972513743128436</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -38643,8 +38746,8 @@
       <c r="G5" s="0" t="s">
         <v>89</v>
       </c>
-      <c r="H5" s="0" t="n">
-        <v>0</v>
+      <c r="H5" s="0">
+        <v>0.0054972513743128436</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -38666,8 +38769,8 @@
       <c r="G6" s="0" t="s">
         <v>91</v>
       </c>
-      <c r="H6" s="0" t="n">
-        <v>0</v>
+      <c r="H6" s="0">
+        <v>0.0054972513743128436</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -38689,8 +38792,8 @@
       <c r="G7" s="0" t="s">
         <v>93</v>
       </c>
-      <c r="H7" s="0" t="n">
-        <v>0</v>
+      <c r="H7" s="0">
+        <v>0.0054972513743128436</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -38712,8 +38815,8 @@
       <c r="G8" s="0" t="s">
         <v>95</v>
       </c>
-      <c r="H8" s="0" t="n">
-        <v>0</v>
+      <c r="H8" s="0">
+        <v>0.0054972513743128436</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -38735,8 +38838,8 @@
       <c r="G9" s="0" t="s">
         <v>97</v>
       </c>
-      <c r="H9" s="0" t="n">
-        <v>0.2805</v>
+      <c r="H9" s="0">
+        <v>0.28585707146426787</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -38758,8 +38861,8 @@
       <c r="G10" s="0" t="s">
         <v>99</v>
       </c>
-      <c r="H10" s="0" t="n">
-        <v>3.707</v>
+      <c r="H10" s="0">
+        <v>3.7106446776611692</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -38781,8 +38884,8 @@
       <c r="G11" s="0" t="s">
         <v>101</v>
       </c>
-      <c r="H11" s="0" t="n">
-        <v>3.333</v>
+      <c r="H11" s="0">
+        <v>3.3368315842078959</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -38804,8 +38907,8 @@
       <c r="G12" s="0" t="s">
         <v>103</v>
       </c>
-      <c r="H12" s="0" t="n">
-        <v>3.036</v>
+      <c r="H12" s="0">
+        <v>3.0399800099950025</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -38821,6 +38924,7 @@
       <c r="G13" s="0" t="s">
         <v>105</v>
       </c>
+      <c r="H13" s="0"/>
     </row>
   </sheetData>
   <printOptions horizontalCentered="false" verticalCentered="false" headings="false" gridLines="false" gridLinesSet="true"/>
@@ -38845,9 +38949,9 @@
     <col min="2" max="2" width="11.99" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
     <col min="3" max="3" width="3.14" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
     <col min="4" max="4" width="22.86" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
-    <col min="6" max="6" width="11.71" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
-    <col min="7" max="7" width="16.29" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
-    <col min="8" max="8" width="22.86" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="6" max="6" width="11.7109375" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="7" max="7" width="16.28515625" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="8" max="8" width="22.85546875" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -38860,6 +38964,7 @@
       <c r="D1" s="0" t="s">
         <v>34</v>
       </c>
+      <c r="F1" s="0"/>
       <c r="G1" s="0" t="s">
         <v>57</v>
       </c>
@@ -38886,8 +38991,8 @@
       <c r="G2" s="0" t="s">
         <v>107</v>
       </c>
-      <c r="H2" s="0" t="n">
-        <v>0</v>
+      <c r="H2" s="0">
+        <v>0.0054972513743128436</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -38909,8 +39014,8 @@
       <c r="G3" s="0" t="s">
         <v>109</v>
       </c>
-      <c r="H3" s="0" t="n">
-        <v>0</v>
+      <c r="H3" s="0">
+        <v>0.0054972513743128436</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -38932,8 +39037,8 @@
       <c r="G4" s="0" t="s">
         <v>111</v>
       </c>
-      <c r="H4" s="0" t="n">
-        <v>0</v>
+      <c r="H4" s="0">
+        <v>0.0054972513743128436</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -38955,8 +39060,8 @@
       <c r="G5" s="0" t="s">
         <v>113</v>
       </c>
-      <c r="H5" s="0" t="n">
-        <v>0</v>
+      <c r="H5" s="0">
+        <v>0.0054972513743128436</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -38978,8 +39083,8 @@
       <c r="G6" s="0" t="s">
         <v>115</v>
       </c>
-      <c r="H6" s="0" t="n">
-        <v>0</v>
+      <c r="H6" s="0">
+        <v>0.0054972513743128436</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -39001,8 +39106,8 @@
       <c r="G7" s="0" t="s">
         <v>117</v>
       </c>
-      <c r="H7" s="0" t="n">
-        <v>0</v>
+      <c r="H7" s="0">
+        <v>0.0054972513743128436</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -39024,8 +39129,8 @@
       <c r="G8" s="0" t="s">
         <v>119</v>
       </c>
-      <c r="H8" s="0" t="n">
-        <v>0</v>
+      <c r="H8" s="0">
+        <v>0.0054972513743128436</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -39047,8 +39152,8 @@
       <c r="G9" s="0" t="s">
         <v>121</v>
       </c>
-      <c r="H9" s="0" t="n">
-        <v>0</v>
+      <c r="H9" s="0">
+        <v>0.0054972513743128436</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -39070,8 +39175,8 @@
       <c r="G10" s="0" t="s">
         <v>123</v>
       </c>
-      <c r="H10" s="0" t="n">
-        <v>0</v>
+      <c r="H10" s="0">
+        <v>0.0054972513743128436</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -39093,8 +39198,8 @@
       <c r="G11" s="0" t="s">
         <v>125</v>
       </c>
-      <c r="H11" s="0" t="n">
-        <v>0</v>
+      <c r="H11" s="0">
+        <v>0.0054972513743128436</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -39116,8 +39221,8 @@
       <c r="G12" s="0" t="s">
         <v>127</v>
       </c>
-      <c r="H12" s="0" t="n">
-        <v>0</v>
+      <c r="H12" s="0">
+        <v>0.0054972513743128436</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -39133,6 +39238,7 @@
       <c r="G13" s="0" t="s">
         <v>129</v>
       </c>
+      <c r="H13" s="0"/>
     </row>
   </sheetData>
   <printOptions horizontalCentered="false" verticalCentered="false" headings="false" gridLines="false" gridLinesSet="true"/>
@@ -39157,9 +39263,9 @@
     <col min="2" max="2" width="11.99" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
     <col min="3" max="3" width="3.14" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
     <col min="4" max="4" width="22.86" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
-    <col min="6" max="6" width="11.71" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
-    <col min="7" max="7" width="16.29" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
-    <col min="8" max="8" width="22.86" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="6" max="6" width="11.7109375" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="7" max="7" width="16.28515625" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="8" max="8" width="22.85546875" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -39172,6 +39278,7 @@
       <c r="D1" s="0" t="s">
         <v>34</v>
       </c>
+      <c r="F1" s="0"/>
       <c r="G1" s="0" t="s">
         <v>57</v>
       </c>
@@ -39198,8 +39305,8 @@
       <c r="G2" s="0" t="s">
         <v>131</v>
       </c>
-      <c r="H2" s="0" t="n">
-        <v>0</v>
+      <c r="H2" s="0">
+        <v>0.0054972513743128436</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -39221,8 +39328,8 @@
       <c r="G3" s="0" t="s">
         <v>133</v>
       </c>
-      <c r="H3" s="0" t="n">
-        <v>0</v>
+      <c r="H3" s="0">
+        <v>0.0054972513743128436</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -39244,8 +39351,8 @@
       <c r="G4" s="0" t="s">
         <v>135</v>
       </c>
-      <c r="H4" s="0" t="n">
-        <v>0</v>
+      <c r="H4" s="0">
+        <v>0.0054972513743128436</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -39267,8 +39374,8 @@
       <c r="G5" s="0" t="s">
         <v>137</v>
       </c>
-      <c r="H5" s="0" t="n">
-        <v>0</v>
+      <c r="H5" s="0">
+        <v>0.0054972513743128436</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -39290,8 +39397,8 @@
       <c r="G6" s="0" t="s">
         <v>139</v>
       </c>
-      <c r="H6" s="0" t="n">
-        <v>0</v>
+      <c r="H6" s="0">
+        <v>0.0054972513743128436</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -39313,8 +39420,8 @@
       <c r="G7" s="0" t="s">
         <v>141</v>
       </c>
-      <c r="H7" s="0" t="n">
-        <v>0</v>
+      <c r="H7" s="0">
+        <v>0.0054972513743128436</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -39336,8 +39443,8 @@
       <c r="G8" s="0" t="s">
         <v>143</v>
       </c>
-      <c r="H8" s="0" t="n">
-        <v>0</v>
+      <c r="H8" s="0">
+        <v>0.0054972513743128436</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -39359,8 +39466,8 @@
       <c r="G9" s="0" t="s">
         <v>145</v>
       </c>
-      <c r="H9" s="0" t="n">
-        <v>0</v>
+      <c r="H9" s="0">
+        <v>0.0054972513743128436</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -39382,8 +39489,8 @@
       <c r="G10" s="0" t="s">
         <v>147</v>
       </c>
-      <c r="H10" s="0" t="n">
-        <v>0</v>
+      <c r="H10" s="0">
+        <v>0.0054972513743128436</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -39405,8 +39512,8 @@
       <c r="G11" s="0" t="s">
         <v>149</v>
       </c>
-      <c r="H11" s="0" t="n">
-        <v>7.799</v>
+      <c r="H11" s="0">
+        <v>7.8005997001499248</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -39428,8 +39535,8 @@
       <c r="G12" s="0" t="s">
         <v>151</v>
       </c>
-      <c r="H12" s="0" t="n">
-        <v>0.3025</v>
+      <c r="H12" s="0">
+        <v>0.30784607696151922</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -39445,6 +39552,7 @@
       <c r="G13" s="0" t="s">
         <v>153</v>
       </c>
+      <c r="H13" s="0"/>
     </row>
   </sheetData>
   <printOptions horizontalCentered="false" verticalCentered="false" headings="false" gridLines="false" gridLinesSet="true"/>
@@ -39469,9 +39577,9 @@
     <col min="2" max="2" width="11.99" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
     <col min="3" max="3" width="3.14" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
     <col min="4" max="4" width="22.86" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
-    <col min="6" max="6" width="11.71" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
-    <col min="7" max="7" width="16.29" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
-    <col min="8" max="8" width="22.86" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="6" max="6" width="11.7109375" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="7" max="7" width="16.28515625" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="8" max="8" width="22.85546875" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -39484,6 +39592,7 @@
       <c r="D1" s="0" t="s">
         <v>34</v>
       </c>
+      <c r="F1" s="0"/>
       <c r="G1" s="0" t="s">
         <v>57</v>
       </c>
@@ -39510,8 +39619,8 @@
       <c r="G2" s="0" t="s">
         <v>155</v>
       </c>
-      <c r="H2" s="0" t="n">
-        <v>1.771</v>
+      <c r="H2" s="0">
+        <v>1.7756121939030485</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -39533,8 +39642,8 @@
       <c r="G3" s="0" t="s">
         <v>157</v>
       </c>
-      <c r="H3" s="0" t="n">
-        <v>0.4895</v>
+      <c r="H3" s="0">
+        <v>0.49475262368815598</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -39556,8 +39665,8 @@
       <c r="G4" s="0" t="s">
         <v>159</v>
       </c>
-      <c r="H4" s="0" t="n">
-        <v>0.4895</v>
+      <c r="H4" s="0">
+        <v>0.49475262368815598</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -39579,8 +39688,8 @@
       <c r="G5" s="0" t="s">
         <v>161</v>
       </c>
-      <c r="H5" s="0" t="n">
-        <v>0.121</v>
+      <c r="H5" s="0">
+        <v>0.12643678160919541</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -39602,8 +39711,8 @@
       <c r="G6" s="0" t="s">
         <v>163</v>
       </c>
-      <c r="H6" s="0" t="n">
-        <v>0</v>
+      <c r="H6" s="0">
+        <v>0.0054972513743128436</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -39625,8 +39734,8 @@
       <c r="G7" s="0" t="s">
         <v>165</v>
       </c>
-      <c r="H7" s="0" t="n">
-        <v>0</v>
+      <c r="H7" s="0">
+        <v>0.0054972513743128436</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -39648,8 +39757,8 @@
       <c r="G8" s="0" t="s">
         <v>167</v>
       </c>
-      <c r="H8" s="0" t="n">
-        <v>0</v>
+      <c r="H8" s="0">
+        <v>0.0054972513743128436</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -39671,8 +39780,8 @@
       <c r="G9" s="0" t="s">
         <v>169</v>
       </c>
-      <c r="H9" s="0" t="n">
-        <v>5.39</v>
+      <c r="H9" s="0">
+        <v>5.3928035982008993</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -39694,8 +39803,8 @@
       <c r="G10" s="0" t="s">
         <v>171</v>
       </c>
-      <c r="H10" s="0" t="n">
-        <v>2.6565</v>
+      <c r="H10" s="0">
+        <v>2.6606696651674162</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -39717,8 +39826,8 @@
       <c r="G11" s="0" t="s">
         <v>173</v>
       </c>
-      <c r="H11" s="0" t="n">
-        <v>0.8085</v>
+      <c r="H11" s="0">
+        <v>0.81359320339830088</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -39740,8 +39849,8 @@
       <c r="G12" s="0" t="s">
         <v>175</v>
       </c>
-      <c r="H12" s="0" t="n">
-        <v>2.761</v>
+      <c r="H12" s="0">
+        <v>2.7651174412793602</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -39757,6 +39866,7 @@
       <c r="G13" s="0" t="s">
         <v>177</v>
       </c>
+      <c r="H13" s="0"/>
     </row>
   </sheetData>
   <printOptions horizontalCentered="false" verticalCentered="false" headings="false" gridLines="false" gridLinesSet="true"/>
@@ -39781,9 +39891,9 @@
     <col min="2" max="2" width="11.99" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
     <col min="3" max="3" width="3.14" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
     <col min="4" max="4" width="22.86" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
-    <col min="6" max="6" width="11.71" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
-    <col min="7" max="7" width="16.29" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
-    <col min="8" max="8" width="22.86" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="6" max="6" width="11.7109375" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="7" max="7" width="16.28515625" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="8" max="8" width="22.85546875" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -39796,6 +39906,7 @@
       <c r="D1" s="0" t="s">
         <v>34</v>
       </c>
+      <c r="F1" s="0"/>
       <c r="G1" s="0" t="s">
         <v>57</v>
       </c>
@@ -39822,8 +39933,8 @@
       <c r="G2" s="0" t="s">
         <v>179</v>
       </c>
-      <c r="H2" s="0" t="n">
-        <v>0</v>
+      <c r="H2" s="0">
+        <v>0.0054972513743128436</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -39845,8 +39956,8 @@
       <c r="G3" s="0" t="s">
         <v>181</v>
       </c>
-      <c r="H3" s="0" t="n">
-        <v>0</v>
+      <c r="H3" s="0">
+        <v>0.0054972513743128436</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -39868,8 +39979,8 @@
       <c r="G4" s="0" t="s">
         <v>183</v>
       </c>
-      <c r="H4" s="0" t="n">
-        <v>0</v>
+      <c r="H4" s="0">
+        <v>0.0054972513743128436</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -39891,8 +40002,8 @@
       <c r="G5" s="0" t="s">
         <v>185</v>
       </c>
-      <c r="H5" s="0" t="n">
-        <v>0</v>
+      <c r="H5" s="0">
+        <v>0.0054972513743128436</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -39914,8 +40025,8 @@
       <c r="G6" s="0" t="s">
         <v>187</v>
       </c>
-      <c r="H6" s="0" t="n">
-        <v>0</v>
+      <c r="H6" s="0">
+        <v>0.0054972513743128436</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -39937,8 +40048,8 @@
       <c r="G7" s="0" t="s">
         <v>189</v>
       </c>
-      <c r="H7" s="0" t="n">
-        <v>0</v>
+      <c r="H7" s="0">
+        <v>0.0054972513743128436</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -39960,8 +40071,8 @@
       <c r="G8" s="0" t="s">
         <v>191</v>
       </c>
-      <c r="H8" s="0" t="n">
-        <v>0</v>
+      <c r="H8" s="0">
+        <v>0.0054972513743128436</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -39983,8 +40094,8 @@
       <c r="G9" s="0" t="s">
         <v>193</v>
       </c>
-      <c r="H9" s="0" t="n">
-        <v>0.033</v>
+      <c r="H9" s="0">
+        <v>0.038480759620189903</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -40006,8 +40117,8 @@
       <c r="G10" s="0" t="s">
         <v>194</v>
       </c>
-      <c r="H10" s="0" t="n">
-        <v>0.0055</v>
+      <c r="H10" s="0">
+        <v>0.010994502748625687</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -40029,8 +40140,8 @@
       <c r="G11" s="0" t="s">
         <v>196</v>
       </c>
-      <c r="H11" s="0" t="n">
-        <v>0</v>
+      <c r="H11" s="0">
+        <v>0.0054972513743128436</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -40052,8 +40163,8 @@
       <c r="G12" s="0" t="s">
         <v>198</v>
       </c>
-      <c r="H12" s="0" t="n">
-        <v>0</v>
+      <c r="H12" s="0">
+        <v>0.0054972513743128436</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -40069,6 +40180,7 @@
       <c r="G13" s="0" t="s">
         <v>200</v>
       </c>
+      <c r="H13" s="0"/>
     </row>
   </sheetData>
   <printOptions horizontalCentered="false" verticalCentered="false" headings="false" gridLines="false" gridLinesSet="true"/>
